--- a/work/batch4/batch4-review.xlsx
+++ b/work/batch4/batch4-review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maost\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\[01] Martin\[07] Claude Code\NS2-Spanish-Translation\work\batch4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D929DA7C-BD20-49F6-9656-4AB7EEABC648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C6E6E0-DAED-4B02-85B8-017080A1DCA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5910" yWindow="690" windowWidth="14070" windowHeight="13845" xr2:uid="{B7159FF6-8F22-4605-95AD-49B5378FEAF5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{B7159FF6-8F22-4605-95AD-49B5378FEAF5}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4763" uniqueCount="2621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="2627">
   <si>
     <t>Section</t>
   </si>
@@ -7929,6 +7929,24 @@
   </si>
   <si>
     <t>Flagged left</t>
+  </si>
+  <si>
+    <t>Use my Spanish</t>
+  </si>
+  <si>
+    <t>Bombardeador defensivo.</t>
+  </si>
+  <si>
+    <t>Puerta de Carga</t>
+  </si>
+  <si>
+    <t>Teletransporta Exotrajes a otra Puerta de Carga</t>
+  </si>
+  <si>
+    <t>Tecnología de Puerta de Carga</t>
+  </si>
+  <si>
+    <t>Desbloquea la tecnología de Puerta de Carga.</t>
   </si>
 </sst>
 </file>
@@ -8489,7 +8507,7 @@
       </c>
       <c r="B10" s="14">
         <f>COUNTA(Review!J2:J775)</f>
-        <v>0</v>
+        <v>774</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -8498,7 +8516,7 @@
       </c>
       <c r="B11" s="14">
         <f>ROWS(Review!J2:J775)-COUNTA(Review!J2:J775)</f>
-        <v>774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -8507,7 +8525,7 @@
       </c>
       <c r="B12" s="14">
         <f>COUNTIFS(Review!G2:G775,"?*",Review!J2:J775,"")</f>
-        <v>233</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8534,7 +8552,7 @@
     <col min="12" max="12" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8598,7 +8616,9 @@
         <v>19</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
@@ -8628,7 +8648,9 @@
         <v>24</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
@@ -8656,7 +8678,9 @@
         <v>30</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
@@ -8684,7 +8708,9 @@
         <v>34</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
@@ -8712,7 +8738,9 @@
         <v>30</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
@@ -8742,7 +8770,9 @@
         <v>42</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
@@ -8770,7 +8800,9 @@
         <v>30</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
@@ -8796,7 +8828,9 @@
       <c r="I9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
@@ -8822,7 +8856,9 @@
       <c r="I10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
@@ -8854,7 +8890,9 @@
       <c r="I11" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
@@ -8884,7 +8922,9 @@
         <v>64</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
@@ -8910,7 +8950,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
@@ -8934,7 +8976,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
@@ -8964,7 +9008,9 @@
         <v>76</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
@@ -8994,7 +9040,9 @@
         <v>81</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
@@ -9020,7 +9068,9 @@
       <c r="G17" s="3"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
@@ -9044,7 +9094,9 @@
       <c r="G18" s="3"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
@@ -9070,7 +9122,9 @@
       <c r="G19" s="3"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
@@ -9094,7 +9148,9 @@
       <c r="G20" s="3"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
@@ -9120,7 +9176,9 @@
       <c r="G21" s="3"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="7"/>
+      <c r="J21" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
@@ -9144,7 +9202,9 @@
       <c r="G22" s="3"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="7"/>
+      <c r="J22" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
@@ -9174,7 +9234,9 @@
         <v>104</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="7"/>
+      <c r="J23" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
@@ -9204,7 +9266,9 @@
         <v>109</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="7"/>
+      <c r="J24" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
@@ -9230,7 +9294,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
@@ -9254,7 +9320,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="7"/>
+      <c r="J26" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
@@ -9284,7 +9352,9 @@
         <v>120</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="7"/>
+      <c r="J27" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
@@ -9308,7 +9378,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="7"/>
+      <c r="J28" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
@@ -9338,7 +9410,9 @@
         <v>120</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="7"/>
+      <c r="J29" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
@@ -9366,7 +9440,9 @@
         <v>130</v>
       </c>
       <c r="I30" s="4"/>
-      <c r="J30" s="7"/>
+      <c r="J30" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
@@ -9396,7 +9472,9 @@
         <v>135</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="7"/>
+      <c r="J31" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
@@ -9424,7 +9502,9 @@
         <v>139</v>
       </c>
       <c r="I32" s="4"/>
-      <c r="J32" s="7"/>
+      <c r="J32" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
@@ -9454,7 +9534,9 @@
         <v>144</v>
       </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="7"/>
+      <c r="J33" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
@@ -9478,7 +9560,9 @@
       <c r="G34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="7"/>
+      <c r="J34" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
@@ -9508,7 +9592,9 @@
         <v>144</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="7"/>
+      <c r="J35" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
@@ -9536,7 +9622,9 @@
         <v>155</v>
       </c>
       <c r="I36" s="4"/>
-      <c r="J36" s="7"/>
+      <c r="J36" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
@@ -9564,7 +9652,9 @@
         <v>159</v>
       </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="7"/>
+      <c r="J37" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
@@ -9594,7 +9684,9 @@
         <v>164</v>
       </c>
       <c r="I38" s="4"/>
-      <c r="J38" s="7"/>
+      <c r="J38" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
@@ -9618,7 +9710,9 @@
       <c r="G39" s="3"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="7"/>
+      <c r="J39" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
@@ -9646,7 +9740,9 @@
         <v>171</v>
       </c>
       <c r="I40" s="4"/>
-      <c r="J40" s="7"/>
+      <c r="J40" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
@@ -9670,7 +9766,9 @@
       <c r="G41" s="3"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="7"/>
+      <c r="J41" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
@@ -9694,7 +9792,9 @@
       <c r="G42" s="3"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="7"/>
+      <c r="J42" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
@@ -9720,7 +9820,9 @@
       <c r="G43" s="3"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="7"/>
+      <c r="J43" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
@@ -9748,7 +9850,9 @@
         <v>184</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="J44" s="7"/>
+      <c r="J44" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
@@ -9772,7 +9876,9 @@
       <c r="G45" s="3"/>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="7"/>
+      <c r="J45" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
@@ -9798,7 +9904,9 @@
       <c r="G46" s="3"/>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="7"/>
+      <c r="J46" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
@@ -9822,7 +9930,9 @@
       <c r="G47" s="3"/>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="7"/>
+      <c r="J47" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
@@ -9846,7 +9956,9 @@
       <c r="G48" s="3"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="7"/>
+      <c r="J48" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
@@ -9876,7 +9988,9 @@
         <v>76</v>
       </c>
       <c r="I49" s="4"/>
-      <c r="J49" s="7"/>
+      <c r="J49" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
@@ -9900,7 +10014,9 @@
       <c r="G50" s="3"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="7"/>
+      <c r="J50" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
@@ -9930,7 +10046,9 @@
         <v>208</v>
       </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="7"/>
+      <c r="J51" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
@@ -9956,7 +10074,9 @@
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="7"/>
+      <c r="J52" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
@@ -9986,7 +10106,9 @@
         <v>216</v>
       </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="7"/>
+      <c r="J53" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
@@ -10012,7 +10134,9 @@
       <c r="I54" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="J54" s="7"/>
+      <c r="J54" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
     </row>
@@ -10042,7 +10166,9 @@
         <v>225</v>
       </c>
       <c r="I55" s="4"/>
-      <c r="J55" s="7"/>
+      <c r="J55" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
@@ -10072,7 +10198,9 @@
         <v>230</v>
       </c>
       <c r="I56" s="4"/>
-      <c r="J56" s="7"/>
+      <c r="J56" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
@@ -10102,7 +10230,9 @@
         <v>235</v>
       </c>
       <c r="I57" s="4"/>
-      <c r="J57" s="7"/>
+      <c r="J57" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
@@ -10130,7 +10260,9 @@
         <v>239</v>
       </c>
       <c r="I58" s="4"/>
-      <c r="J58" s="7"/>
+      <c r="J58" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
@@ -10160,7 +10292,9 @@
         <v>244</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="7"/>
+      <c r="J59" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
@@ -10186,7 +10320,9 @@
       <c r="I60" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="J60" s="7"/>
+      <c r="J60" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
@@ -10210,7 +10346,9 @@
       <c r="G61" s="3"/>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="7"/>
+      <c r="J61" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
@@ -10234,7 +10372,9 @@
       <c r="G62" s="3"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="7"/>
+      <c r="J62" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
@@ -10258,7 +10398,9 @@
       <c r="G63" s="3"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="7"/>
+      <c r="J63" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
@@ -10282,7 +10424,9 @@
       <c r="G64" s="3"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="7"/>
+      <c r="J64" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
@@ -10306,7 +10450,9 @@
       <c r="G65" s="3"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="7"/>
+      <c r="J65" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
@@ -10334,7 +10480,9 @@
         <v>267</v>
       </c>
       <c r="I66" s="4"/>
-      <c r="J66" s="7"/>
+      <c r="J66" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
@@ -10360,7 +10508,9 @@
       <c r="G67" s="3"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="7"/>
+      <c r="J67" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
@@ -10384,7 +10534,9 @@
       <c r="G68" s="3"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="7"/>
+      <c r="J68" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
@@ -10410,7 +10562,9 @@
       <c r="G69" s="3"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="7"/>
+      <c r="J69" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
@@ -10434,7 +10588,9 @@
       <c r="G70" s="3"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="7"/>
+      <c r="J70" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
     </row>
@@ -10460,7 +10616,9 @@
       <c r="G71" s="3"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="7"/>
+      <c r="J71" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
@@ -10490,7 +10648,9 @@
       <c r="I72" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="J72" s="7"/>
+      <c r="J72" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
@@ -10514,7 +10674,9 @@
       <c r="G73" s="3"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="7"/>
+      <c r="J73" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
@@ -10538,7 +10700,9 @@
       <c r="G74" s="3"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="7"/>
+      <c r="J74" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
@@ -10568,7 +10732,9 @@
         <v>298</v>
       </c>
       <c r="I75" s="4"/>
-      <c r="J75" s="7"/>
+      <c r="J75" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
@@ -10592,7 +10758,9 @@
       <c r="G76" s="3"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="7"/>
+      <c r="J76" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
@@ -10622,7 +10790,9 @@
         <v>306</v>
       </c>
       <c r="I77" s="4"/>
-      <c r="J77" s="7"/>
+      <c r="J77" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
@@ -10646,7 +10816,9 @@
       <c r="G78" s="3"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="7"/>
+      <c r="J78" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
@@ -10672,7 +10844,9 @@
       <c r="G79" s="3"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="7"/>
+      <c r="J79" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
@@ -10696,7 +10870,9 @@
       <c r="G80" s="3"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="7"/>
+      <c r="J80" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
@@ -10720,7 +10896,9 @@
       <c r="G81" s="3"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="7"/>
+      <c r="J81" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
@@ -10748,7 +10926,9 @@
         <v>323</v>
       </c>
       <c r="I82" s="4"/>
-      <c r="J82" s="7"/>
+      <c r="J82" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
@@ -10772,7 +10952,9 @@
       <c r="G83" s="3"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="7"/>
+      <c r="J83" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
@@ -10796,7 +10978,9 @@
       <c r="G84" s="3"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="7"/>
+      <c r="J84" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
@@ -10826,7 +11010,9 @@
         <v>334</v>
       </c>
       <c r="I85" s="4"/>
-      <c r="J85" s="7"/>
+      <c r="J85" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
@@ -10850,7 +11036,9 @@
       <c r="G86" s="3"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="7"/>
+      <c r="J86" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
@@ -10880,7 +11068,9 @@
         <v>342</v>
       </c>
       <c r="I87" s="4"/>
-      <c r="J87" s="7"/>
+      <c r="J87" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
@@ -10904,7 +11094,9 @@
       <c r="G88" s="3"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="7"/>
+      <c r="J88" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
@@ -10934,7 +11126,9 @@
         <v>350</v>
       </c>
       <c r="I89" s="4"/>
-      <c r="J89" s="7"/>
+      <c r="J89" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
@@ -10960,7 +11154,9 @@
       <c r="I90" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="J90" s="7"/>
+      <c r="J90" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
@@ -10984,7 +11180,9 @@
       <c r="G91" s="3"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
-      <c r="J91" s="7"/>
+      <c r="J91" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
@@ -11008,7 +11206,9 @@
       <c r="G92" s="3"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
-      <c r="J92" s="7"/>
+      <c r="J92" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
@@ -11032,7 +11232,9 @@
       <c r="G93" s="3"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="7"/>
+      <c r="J93" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
@@ -11056,7 +11258,9 @@
       <c r="G94" s="3"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="7"/>
+      <c r="J94" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
@@ -11080,7 +11284,9 @@
       <c r="G95" s="3"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="7"/>
+      <c r="J95" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
@@ -11104,7 +11310,9 @@
       <c r="G96" s="3"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="7"/>
+      <c r="J96" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
@@ -11134,7 +11342,9 @@
         <v>377</v>
       </c>
       <c r="I97" s="4"/>
-      <c r="J97" s="7"/>
+      <c r="J97" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
@@ -11160,7 +11370,9 @@
       <c r="G98" s="3"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="7"/>
+      <c r="J98" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
@@ -11192,7 +11404,9 @@
       <c r="I99" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="J99" s="7"/>
+      <c r="J99" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
@@ -11216,7 +11430,9 @@
       <c r="G100" s="3"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="7"/>
+      <c r="J100" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
@@ -11242,7 +11458,9 @@
       <c r="G101" s="3"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="7"/>
+      <c r="J101" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
@@ -11266,7 +11484,9 @@
       <c r="G102" s="3"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="7"/>
+      <c r="J102" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
@@ -11296,7 +11516,9 @@
         <v>397</v>
       </c>
       <c r="I103" s="4"/>
-      <c r="J103" s="7"/>
+      <c r="J103" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
@@ -11320,7 +11542,9 @@
       <c r="G104" s="3"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="7"/>
+      <c r="J104" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
@@ -11350,7 +11574,9 @@
         <v>405</v>
       </c>
       <c r="I105" s="4"/>
-      <c r="J105" s="7"/>
+      <c r="J105" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
@@ -11378,7 +11604,9 @@
         <v>409</v>
       </c>
       <c r="I106" s="4"/>
-      <c r="J106" s="7"/>
+      <c r="J106" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
@@ -11408,7 +11636,9 @@
         <v>414</v>
       </c>
       <c r="I107" s="4"/>
-      <c r="J107" s="7"/>
+      <c r="J107" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
@@ -11432,7 +11662,9 @@
       <c r="G108" s="3"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="7"/>
+      <c r="J108" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
@@ -11456,7 +11688,9 @@
       <c r="G109" s="3"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="7"/>
+      <c r="J109" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
@@ -11484,7 +11718,9 @@
         <v>424</v>
       </c>
       <c r="I110" s="4"/>
-      <c r="J110" s="7"/>
+      <c r="J110" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
@@ -11508,7 +11744,9 @@
       <c r="G111" s="3"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="7"/>
+      <c r="J111" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
@@ -11534,7 +11772,9 @@
       <c r="G112" s="3"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="7"/>
+      <c r="J112" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
@@ -11558,7 +11798,9 @@
       <c r="G113" s="3"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
-      <c r="J113" s="7"/>
+      <c r="J113" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
     </row>
@@ -11584,7 +11826,9 @@
       <c r="G114" s="3"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
-      <c r="J114" s="7"/>
+      <c r="J114" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K114" s="8"/>
       <c r="L114" s="8"/>
     </row>
@@ -11614,7 +11858,9 @@
         <v>441</v>
       </c>
       <c r="I115" s="4"/>
-      <c r="J115" s="7"/>
+      <c r="J115" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
     </row>
@@ -11638,7 +11884,9 @@
       <c r="G116" s="3"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="7"/>
+      <c r="J116" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
     </row>
@@ -11668,7 +11916,9 @@
         <v>449</v>
       </c>
       <c r="I117" s="4"/>
-      <c r="J117" s="7"/>
+      <c r="J117" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
     </row>
@@ -11692,7 +11942,9 @@
       <c r="G118" s="3"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="7"/>
+      <c r="J118" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
     </row>
@@ -11716,7 +11968,9 @@
       <c r="G119" s="3"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
-      <c r="J119" s="7"/>
+      <c r="J119" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
     </row>
@@ -11740,7 +11994,9 @@
       <c r="G120" s="3"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
-      <c r="J120" s="7"/>
+      <c r="J120" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K120" s="8"/>
       <c r="L120" s="8"/>
     </row>
@@ -11764,7 +12020,9 @@
       <c r="G121" s="3"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
-      <c r="J121" s="7"/>
+      <c r="J121" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K121" s="8"/>
       <c r="L121" s="8"/>
     </row>
@@ -11794,8 +12052,12 @@
         <v>466</v>
       </c>
       <c r="I122" s="4"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="8"/>
+      <c r="J122" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>464</v>
+      </c>
       <c r="L122" s="8"/>
     </row>
     <row r="123" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -11824,7 +12086,9 @@
         <v>471</v>
       </c>
       <c r="I123" s="4"/>
-      <c r="J123" s="7"/>
+      <c r="J123" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K123" s="8"/>
       <c r="L123" s="8"/>
     </row>
@@ -11852,7 +12116,9 @@
         <v>475</v>
       </c>
       <c r="I124" s="4"/>
-      <c r="J124" s="7"/>
+      <c r="J124" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
     </row>
@@ -11876,7 +12142,9 @@
       <c r="G125" s="3"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
-      <c r="J125" s="7"/>
+      <c r="J125" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K125" s="8"/>
       <c r="L125" s="8"/>
     </row>
@@ -11900,7 +12168,9 @@
       <c r="G126" s="3"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
-      <c r="J126" s="7"/>
+      <c r="J126" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K126" s="8"/>
       <c r="L126" s="8"/>
     </row>
@@ -11928,7 +12198,9 @@
         <v>485</v>
       </c>
       <c r="I127" s="4"/>
-      <c r="J127" s="7"/>
+      <c r="J127" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K127" s="8"/>
       <c r="L127" s="8"/>
     </row>
@@ -11952,7 +12224,9 @@
       <c r="G128" s="3"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
-      <c r="J128" s="7"/>
+      <c r="J128" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K128" s="8"/>
       <c r="L128" s="8"/>
     </row>
@@ -11976,7 +12250,9 @@
       <c r="G129" s="3"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
-      <c r="J129" s="7"/>
+      <c r="J129" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K129" s="8"/>
       <c r="L129" s="8"/>
     </row>
@@ -12000,7 +12276,9 @@
       <c r="G130" s="3"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
-      <c r="J130" s="7"/>
+      <c r="J130" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
     </row>
@@ -12024,7 +12302,9 @@
       <c r="G131" s="3"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
-      <c r="J131" s="7"/>
+      <c r="J131" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
     </row>
@@ -12048,7 +12328,9 @@
       <c r="G132" s="3"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
-      <c r="J132" s="7"/>
+      <c r="J132" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
     </row>
@@ -12072,7 +12354,9 @@
       <c r="G133" s="3"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
-      <c r="J133" s="7"/>
+      <c r="J133" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
     </row>
@@ -12098,7 +12382,9 @@
       <c r="I134" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="J134" s="7"/>
+      <c r="J134" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
     </row>
@@ -12122,7 +12408,9 @@
       <c r="G135" s="3"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
-      <c r="J135" s="7"/>
+      <c r="J135" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
@@ -12146,7 +12434,9 @@
       <c r="G136" s="3"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
-      <c r="J136" s="7"/>
+      <c r="J136" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K136" s="8"/>
       <c r="L136" s="8"/>
     </row>
@@ -12174,7 +12464,9 @@
       <c r="I137" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J137" s="7"/>
+      <c r="J137" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
@@ -12202,7 +12494,9 @@
       <c r="I138" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="J138" s="7"/>
+      <c r="J138" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
     </row>
@@ -12228,7 +12522,9 @@
       <c r="G139" s="3"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
-      <c r="J139" s="7"/>
+      <c r="J139" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
@@ -12254,7 +12550,9 @@
       <c r="G140" s="3"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
-      <c r="J140" s="7"/>
+      <c r="J140" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
     </row>
@@ -12284,7 +12582,9 @@
         <v>533</v>
       </c>
       <c r="I141" s="4"/>
-      <c r="J141" s="7"/>
+      <c r="J141" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
@@ -12310,7 +12610,9 @@
       <c r="G142" s="3"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
-      <c r="J142" s="7"/>
+      <c r="J142" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
     </row>
@@ -12336,7 +12638,9 @@
       <c r="G143" s="3"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
-      <c r="J143" s="7"/>
+      <c r="J143" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
@@ -12362,7 +12666,9 @@
       <c r="G144" s="3"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
-      <c r="J144" s="7"/>
+      <c r="J144" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
     </row>
@@ -12388,7 +12694,9 @@
       <c r="G145" s="3"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
-      <c r="J145" s="7"/>
+      <c r="J145" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
     </row>
@@ -12418,7 +12726,9 @@
         <v>550</v>
       </c>
       <c r="I146" s="4"/>
-      <c r="J146" s="7"/>
+      <c r="J146" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
     </row>
@@ -12442,7 +12752,9 @@
       <c r="G147" s="3"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
-      <c r="J147" s="7"/>
+      <c r="J147" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
     </row>
@@ -12472,7 +12784,9 @@
         <v>558</v>
       </c>
       <c r="I148" s="4"/>
-      <c r="J148" s="7"/>
+      <c r="J148" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K148" s="8"/>
       <c r="L148" s="8"/>
     </row>
@@ -12502,7 +12816,9 @@
         <v>563</v>
       </c>
       <c r="I149" s="4"/>
-      <c r="J149" s="7"/>
+      <c r="J149" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
     </row>
@@ -12532,7 +12848,9 @@
         <v>563</v>
       </c>
       <c r="I150" s="4"/>
-      <c r="J150" s="7"/>
+      <c r="J150" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K150" s="8"/>
       <c r="L150" s="8"/>
     </row>
@@ -12562,7 +12880,9 @@
         <v>563</v>
       </c>
       <c r="I151" s="4"/>
-      <c r="J151" s="7"/>
+      <c r="J151" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
     </row>
@@ -12592,7 +12912,9 @@
         <v>576</v>
       </c>
       <c r="I152" s="4"/>
-      <c r="J152" s="7"/>
+      <c r="J152" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
     </row>
@@ -12622,7 +12944,9 @@
         <v>581</v>
       </c>
       <c r="I153" s="4"/>
-      <c r="J153" s="7"/>
+      <c r="J153" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
     </row>
@@ -12652,7 +12976,9 @@
         <v>586</v>
       </c>
       <c r="I154" s="4"/>
-      <c r="J154" s="7"/>
+      <c r="J154" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K154" s="8"/>
       <c r="L154" s="8"/>
     </row>
@@ -12678,7 +13004,9 @@
       <c r="G155" s="3"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
-      <c r="J155" s="7"/>
+      <c r="J155" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
     </row>
@@ -12708,7 +13036,9 @@
         <v>594</v>
       </c>
       <c r="I156" s="4"/>
-      <c r="J156" s="7"/>
+      <c r="J156" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K156" s="8"/>
       <c r="L156" s="8"/>
     </row>
@@ -12738,7 +13068,9 @@
         <v>599</v>
       </c>
       <c r="I157" s="4"/>
-      <c r="J157" s="7"/>
+      <c r="J157" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
     </row>
@@ -12768,7 +13100,9 @@
         <v>604</v>
       </c>
       <c r="I158" s="4"/>
-      <c r="J158" s="7"/>
+      <c r="J158" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K158" s="8"/>
       <c r="L158" s="8"/>
     </row>
@@ -12798,7 +13132,9 @@
         <v>604</v>
       </c>
       <c r="I159" s="4"/>
-      <c r="J159" s="7"/>
+      <c r="J159" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K159" s="8"/>
       <c r="L159" s="8"/>
     </row>
@@ -12828,7 +13164,9 @@
         <v>612</v>
       </c>
       <c r="I160" s="4"/>
-      <c r="J160" s="7"/>
+      <c r="J160" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K160" s="8"/>
       <c r="L160" s="8"/>
     </row>
@@ -12854,7 +13192,9 @@
       <c r="G161" s="3"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
-      <c r="J161" s="7"/>
+      <c r="J161" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K161" s="8"/>
       <c r="L161" s="8"/>
     </row>
@@ -12884,7 +13224,9 @@
         <v>563</v>
       </c>
       <c r="I162" s="4"/>
-      <c r="J162" s="7"/>
+      <c r="J162" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K162" s="8"/>
       <c r="L162" s="8"/>
     </row>
@@ -12914,7 +13256,9 @@
         <v>563</v>
       </c>
       <c r="I163" s="4"/>
-      <c r="J163" s="7"/>
+      <c r="J163" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K163" s="8"/>
       <c r="L163" s="8"/>
     </row>
@@ -12940,7 +13284,9 @@
       <c r="G164" s="3"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
-      <c r="J164" s="7"/>
+      <c r="J164" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K164" s="8"/>
       <c r="L164" s="8"/>
     </row>
@@ -12970,7 +13316,9 @@
         <v>563</v>
       </c>
       <c r="I165" s="4"/>
-      <c r="J165" s="7"/>
+      <c r="J165" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K165" s="8"/>
       <c r="L165" s="8"/>
     </row>
@@ -13000,7 +13348,9 @@
         <v>563</v>
       </c>
       <c r="I166" s="4"/>
-      <c r="J166" s="7"/>
+      <c r="J166" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K166" s="8"/>
       <c r="L166" s="8"/>
     </row>
@@ -13030,7 +13380,9 @@
         <v>639</v>
       </c>
       <c r="I167" s="4"/>
-      <c r="J167" s="7"/>
+      <c r="J167" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K167" s="8"/>
       <c r="L167" s="8"/>
     </row>
@@ -13060,7 +13412,9 @@
         <v>563</v>
       </c>
       <c r="I168" s="4"/>
-      <c r="J168" s="7"/>
+      <c r="J168" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K168" s="8"/>
       <c r="L168" s="8"/>
     </row>
@@ -13090,7 +13444,9 @@
         <v>648</v>
       </c>
       <c r="I169" s="4"/>
-      <c r="J169" s="7"/>
+      <c r="J169" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
     </row>
@@ -13116,7 +13472,9 @@
       <c r="G170" s="3"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
-      <c r="J170" s="7"/>
+      <c r="J170" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K170" s="8"/>
       <c r="L170" s="8"/>
     </row>
@@ -13146,7 +13504,9 @@
         <v>656</v>
       </c>
       <c r="I171" s="4"/>
-      <c r="J171" s="7"/>
+      <c r="J171" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K171" s="8"/>
       <c r="L171" s="8"/>
     </row>
@@ -13176,7 +13536,9 @@
         <v>656</v>
       </c>
       <c r="I172" s="4"/>
-      <c r="J172" s="7"/>
+      <c r="J172" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K172" s="8"/>
       <c r="L172" s="8"/>
     </row>
@@ -13206,7 +13568,9 @@
         <v>563</v>
       </c>
       <c r="I173" s="4"/>
-      <c r="J173" s="7"/>
+      <c r="J173" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K173" s="8"/>
       <c r="L173" s="8"/>
     </row>
@@ -13232,7 +13596,9 @@
       <c r="G174" s="3"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
-      <c r="J174" s="7"/>
+      <c r="J174" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K174" s="8"/>
       <c r="L174" s="8"/>
     </row>
@@ -13262,7 +13628,9 @@
         <v>563</v>
       </c>
       <c r="I175" s="4"/>
-      <c r="J175" s="7"/>
+      <c r="J175" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
     </row>
@@ -13288,7 +13656,9 @@
       <c r="G176" s="3"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
-      <c r="J176" s="7"/>
+      <c r="J176" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K176" s="8"/>
       <c r="L176" s="8"/>
     </row>
@@ -13318,7 +13688,9 @@
         <v>679</v>
       </c>
       <c r="I177" s="4"/>
-      <c r="J177" s="7"/>
+      <c r="J177" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
     </row>
@@ -13348,7 +13720,9 @@
         <v>684</v>
       </c>
       <c r="I178" s="4"/>
-      <c r="J178" s="7"/>
+      <c r="J178" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K178" s="8"/>
       <c r="L178" s="8"/>
     </row>
@@ -13378,7 +13752,9 @@
         <v>689</v>
       </c>
       <c r="I179" s="4"/>
-      <c r="J179" s="7"/>
+      <c r="J179" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
     </row>
@@ -13408,7 +13784,9 @@
         <v>694</v>
       </c>
       <c r="I180" s="4"/>
-      <c r="J180" s="7"/>
+      <c r="J180" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K180" s="8"/>
       <c r="L180" s="8"/>
     </row>
@@ -13438,7 +13816,9 @@
         <v>699</v>
       </c>
       <c r="I181" s="4"/>
-      <c r="J181" s="7"/>
+      <c r="J181" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
     </row>
@@ -13468,7 +13848,9 @@
         <v>563</v>
       </c>
       <c r="I182" s="4"/>
-      <c r="J182" s="7"/>
+      <c r="J182" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K182" s="8"/>
       <c r="L182" s="8"/>
     </row>
@@ -13498,7 +13880,9 @@
         <v>563</v>
       </c>
       <c r="I183" s="4"/>
-      <c r="J183" s="7"/>
+      <c r="J183" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
     </row>
@@ -13528,7 +13912,9 @@
         <v>563</v>
       </c>
       <c r="I184" s="4"/>
-      <c r="J184" s="7"/>
+      <c r="J184" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K184" s="8"/>
       <c r="L184" s="8"/>
     </row>
@@ -13558,7 +13944,9 @@
         <v>716</v>
       </c>
       <c r="I185" s="4"/>
-      <c r="J185" s="7"/>
+      <c r="J185" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
     </row>
@@ -13588,7 +13976,9 @@
         <v>721</v>
       </c>
       <c r="I186" s="4"/>
-      <c r="J186" s="7"/>
+      <c r="J186" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
     </row>
@@ -13618,7 +14008,9 @@
         <v>726</v>
       </c>
       <c r="I187" s="4"/>
-      <c r="J187" s="7"/>
+      <c r="J187" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K187" s="8"/>
       <c r="L187" s="8"/>
     </row>
@@ -13642,7 +14034,9 @@
       <c r="G188" s="3"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
-      <c r="J188" s="7"/>
+      <c r="J188" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
     </row>
@@ -13670,7 +14064,9 @@
         <v>731</v>
       </c>
       <c r="I189" s="4"/>
-      <c r="J189" s="7"/>
+      <c r="J189" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
     </row>
@@ -13698,7 +14094,9 @@
         <v>736</v>
       </c>
       <c r="I190" s="4"/>
-      <c r="J190" s="7"/>
+      <c r="J190" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
     </row>
@@ -13728,7 +14126,9 @@
         <v>741</v>
       </c>
       <c r="I191" s="4"/>
-      <c r="J191" s="7"/>
+      <c r="J191" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K191" s="8"/>
       <c r="L191" s="8"/>
     </row>
@@ -13758,7 +14158,9 @@
         <v>746</v>
       </c>
       <c r="I192" s="4"/>
-      <c r="J192" s="7"/>
+      <c r="J192" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
     </row>
@@ -13788,7 +14190,9 @@
         <v>751</v>
       </c>
       <c r="I193" s="4"/>
-      <c r="J193" s="7"/>
+      <c r="J193" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
     </row>
@@ -13818,7 +14222,9 @@
         <v>756</v>
       </c>
       <c r="I194" s="4"/>
-      <c r="J194" s="7"/>
+      <c r="J194" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
     </row>
@@ -13848,7 +14254,9 @@
         <v>761</v>
       </c>
       <c r="I195" s="4"/>
-      <c r="J195" s="7"/>
+      <c r="J195" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
     </row>
@@ -13872,7 +14280,9 @@
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
-      <c r="J196" s="7"/>
+      <c r="J196" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
     </row>
@@ -13902,7 +14312,9 @@
         <v>769</v>
       </c>
       <c r="I197" s="4"/>
-      <c r="J197" s="7"/>
+      <c r="J197" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
     </row>
@@ -13928,7 +14340,9 @@
       <c r="G198" s="3"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
-      <c r="J198" s="7"/>
+      <c r="J198" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K198" s="8"/>
       <c r="L198" s="8"/>
     </row>
@@ -13954,7 +14368,9 @@
       <c r="G199" s="3"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
-      <c r="J199" s="7"/>
+      <c r="J199" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K199" s="8"/>
       <c r="L199" s="8"/>
     </row>
@@ -13984,7 +14400,9 @@
         <v>746</v>
       </c>
       <c r="I200" s="4"/>
-      <c r="J200" s="7"/>
+      <c r="J200" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K200" s="8"/>
       <c r="L200" s="8"/>
     </row>
@@ -14014,7 +14432,9 @@
         <v>746</v>
       </c>
       <c r="I201" s="4"/>
-      <c r="J201" s="7"/>
+      <c r="J201" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K201" s="8"/>
       <c r="L201" s="8"/>
     </row>
@@ -14044,7 +14464,9 @@
         <v>746</v>
       </c>
       <c r="I202" s="4"/>
-      <c r="J202" s="7"/>
+      <c r="J202" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K202" s="8"/>
       <c r="L202" s="8"/>
     </row>
@@ -14074,7 +14496,9 @@
         <v>746</v>
       </c>
       <c r="I203" s="4"/>
-      <c r="J203" s="7"/>
+      <c r="J203" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K203" s="8"/>
       <c r="L203" s="8"/>
     </row>
@@ -14104,7 +14528,9 @@
         <v>793</v>
       </c>
       <c r="I204" s="4"/>
-      <c r="J204" s="7"/>
+      <c r="J204" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
     </row>
@@ -14130,7 +14556,9 @@
       <c r="G205" s="3"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
-      <c r="J205" s="7"/>
+      <c r="J205" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
@@ -14160,7 +14588,9 @@
         <v>769</v>
       </c>
       <c r="I206" s="4"/>
-      <c r="J206" s="7"/>
+      <c r="J206" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
     </row>
@@ -14190,7 +14620,9 @@
         <v>802</v>
       </c>
       <c r="I207" s="4"/>
-      <c r="J207" s="7"/>
+      <c r="J207" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K207" s="8"/>
       <c r="L207" s="8"/>
     </row>
@@ -14222,7 +14654,9 @@
       <c r="I208" s="10" t="s">
         <v>808</v>
       </c>
-      <c r="J208" s="7"/>
+      <c r="J208" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K208" s="8"/>
       <c r="L208" s="8"/>
     </row>
@@ -14246,7 +14680,9 @@
       <c r="G209" s="3"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
-      <c r="J209" s="7"/>
+      <c r="J209" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K209" s="8"/>
       <c r="L209" s="8"/>
     </row>
@@ -14270,7 +14706,9 @@
       <c r="G210" s="3"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
-      <c r="J210" s="7"/>
+      <c r="J210" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K210" s="8"/>
       <c r="L210" s="8"/>
     </row>
@@ -14296,7 +14734,9 @@
       <c r="G211" s="3"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
-      <c r="J211" s="7"/>
+      <c r="J211" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K211" s="8"/>
       <c r="L211" s="8"/>
     </row>
@@ -14322,7 +14762,9 @@
       <c r="G212" s="3"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
-      <c r="J212" s="7"/>
+      <c r="J212" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K212" s="8"/>
       <c r="L212" s="8"/>
     </row>
@@ -14348,7 +14790,9 @@
       <c r="G213" s="3"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
-      <c r="J213" s="7"/>
+      <c r="J213" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K213" s="8"/>
       <c r="L213" s="8"/>
     </row>
@@ -14376,7 +14820,9 @@
         <v>826</v>
       </c>
       <c r="I214" s="4"/>
-      <c r="J214" s="7"/>
+      <c r="J214" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K214" s="8"/>
       <c r="L214" s="8"/>
     </row>
@@ -14404,7 +14850,9 @@
         <v>830</v>
       </c>
       <c r="I215" s="4"/>
-      <c r="J215" s="7"/>
+      <c r="J215" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K215" s="8"/>
       <c r="L215" s="8"/>
     </row>
@@ -14432,7 +14880,9 @@
         <v>830</v>
       </c>
       <c r="I216" s="4"/>
-      <c r="J216" s="7"/>
+      <c r="J216" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K216" s="8"/>
       <c r="L216" s="8"/>
     </row>
@@ -14456,7 +14906,9 @@
       <c r="G217" s="3"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
-      <c r="J217" s="7"/>
+      <c r="J217" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K217" s="8"/>
       <c r="L217" s="8"/>
     </row>
@@ -14480,7 +14932,9 @@
       <c r="G218" s="3"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
-      <c r="J218" s="7"/>
+      <c r="J218" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K218" s="8"/>
       <c r="L218" s="8"/>
     </row>
@@ -14504,7 +14958,9 @@
       <c r="G219" s="3"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
-      <c r="J219" s="7"/>
+      <c r="J219" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K219" s="8"/>
       <c r="L219" s="8"/>
     </row>
@@ -14534,7 +14990,9 @@
         <v>847</v>
       </c>
       <c r="I220" s="4"/>
-      <c r="J220" s="7"/>
+      <c r="J220" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K220" s="8"/>
       <c r="L220" s="8"/>
     </row>
@@ -14564,7 +15022,9 @@
         <v>852</v>
       </c>
       <c r="I221" s="4"/>
-      <c r="J221" s="7"/>
+      <c r="J221" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K221" s="8"/>
       <c r="L221" s="8"/>
     </row>
@@ -14594,7 +15054,9 @@
         <v>857</v>
       </c>
       <c r="I222" s="4"/>
-      <c r="J222" s="7"/>
+      <c r="J222" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K222" s="8"/>
       <c r="L222" s="8"/>
     </row>
@@ -14622,7 +15084,9 @@
         <v>861</v>
       </c>
       <c r="I223" s="4"/>
-      <c r="J223" s="7"/>
+      <c r="J223" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K223" s="8"/>
       <c r="L223" s="8"/>
     </row>
@@ -14652,7 +15116,9 @@
         <v>866</v>
       </c>
       <c r="I224" s="4"/>
-      <c r="J224" s="7"/>
+      <c r="J224" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K224" s="8"/>
       <c r="L224" s="8"/>
     </row>
@@ -14682,7 +15148,9 @@
         <v>871</v>
       </c>
       <c r="I225" s="4"/>
-      <c r="J225" s="7"/>
+      <c r="J225" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K225" s="8"/>
       <c r="L225" s="8"/>
     </row>
@@ -14712,7 +15180,9 @@
         <v>876</v>
       </c>
       <c r="I226" s="4"/>
-      <c r="J226" s="7"/>
+      <c r="J226" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K226" s="8"/>
       <c r="L226" s="8"/>
     </row>
@@ -14742,7 +15212,9 @@
         <v>881</v>
       </c>
       <c r="I227" s="4"/>
-      <c r="J227" s="7"/>
+      <c r="J227" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K227" s="8"/>
       <c r="L227" s="8"/>
     </row>
@@ -14772,7 +15244,9 @@
         <v>886</v>
       </c>
       <c r="I228" s="4"/>
-      <c r="J228" s="7"/>
+      <c r="J228" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K228" s="8"/>
       <c r="L228" s="8"/>
     </row>
@@ -14796,7 +15270,9 @@
       <c r="G229" s="3"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
-      <c r="J229" s="7"/>
+      <c r="J229" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K229" s="8"/>
       <c r="L229" s="8"/>
     </row>
@@ -14826,7 +15302,9 @@
         <v>894</v>
       </c>
       <c r="I230" s="4"/>
-      <c r="J230" s="7"/>
+      <c r="J230" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K230" s="8"/>
       <c r="L230" s="8"/>
     </row>
@@ -14856,7 +15334,9 @@
         <v>899</v>
       </c>
       <c r="I231" s="4"/>
-      <c r="J231" s="7"/>
+      <c r="J231" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K231" s="8"/>
       <c r="L231" s="8"/>
     </row>
@@ -14886,7 +15366,9 @@
         <v>904</v>
       </c>
       <c r="I232" s="4"/>
-      <c r="J232" s="7"/>
+      <c r="J232" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K232" s="8"/>
       <c r="L232" s="8"/>
     </row>
@@ -14916,7 +15398,9 @@
         <v>909</v>
       </c>
       <c r="I233" s="4"/>
-      <c r="J233" s="7"/>
+      <c r="J233" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K233" s="8"/>
       <c r="L233" s="8"/>
     </row>
@@ -14944,7 +15428,9 @@
         <v>913</v>
       </c>
       <c r="I234" s="4"/>
-      <c r="J234" s="7"/>
+      <c r="J234" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K234" s="8"/>
       <c r="L234" s="8"/>
     </row>
@@ -14974,7 +15460,9 @@
         <v>918</v>
       </c>
       <c r="I235" s="4"/>
-      <c r="J235" s="7"/>
+      <c r="J235" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K235" s="8"/>
       <c r="L235" s="8"/>
     </row>
@@ -15004,7 +15492,9 @@
         <v>923</v>
       </c>
       <c r="I236" s="4"/>
-      <c r="J236" s="7"/>
+      <c r="J236" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K236" s="8"/>
       <c r="L236" s="8"/>
     </row>
@@ -15034,7 +15524,9 @@
         <v>928</v>
       </c>
       <c r="I237" s="4"/>
-      <c r="J237" s="7"/>
+      <c r="J237" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K237" s="8"/>
       <c r="L237" s="8"/>
     </row>
@@ -15058,7 +15550,9 @@
       <c r="G238" s="3"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
-      <c r="J238" s="7"/>
+      <c r="J238" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K238" s="8"/>
       <c r="L238" s="8"/>
     </row>
@@ -15082,7 +15576,9 @@
       <c r="G239" s="3"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
-      <c r="J239" s="7"/>
+      <c r="J239" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K239" s="8"/>
       <c r="L239" s="8"/>
     </row>
@@ -15106,7 +15602,9 @@
       <c r="G240" s="3"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
-      <c r="J240" s="7"/>
+      <c r="J240" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K240" s="8"/>
       <c r="L240" s="8"/>
     </row>
@@ -15130,7 +15628,9 @@
       <c r="G241" s="3"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
-      <c r="J241" s="7"/>
+      <c r="J241" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K241" s="8"/>
       <c r="L241" s="8"/>
     </row>
@@ -15154,7 +15654,9 @@
       <c r="G242" s="3"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
-      <c r="J242" s="7"/>
+      <c r="J242" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K242" s="8"/>
       <c r="L242" s="8"/>
     </row>
@@ -15182,7 +15684,9 @@
         <v>947</v>
       </c>
       <c r="I243" s="4"/>
-      <c r="J243" s="7"/>
+      <c r="J243" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K243" s="8"/>
       <c r="L243" s="8"/>
     </row>
@@ -15210,7 +15714,9 @@
         <v>830</v>
       </c>
       <c r="I244" s="4"/>
-      <c r="J244" s="7"/>
+      <c r="J244" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K244" s="8"/>
       <c r="L244" s="8"/>
     </row>
@@ -15234,7 +15740,9 @@
       <c r="G245" s="3"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
-      <c r="J245" s="7"/>
+      <c r="J245" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K245" s="8"/>
       <c r="L245" s="8"/>
     </row>
@@ -15258,7 +15766,9 @@
       <c r="G246" s="3"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
-      <c r="J246" s="7"/>
+      <c r="J246" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K246" s="8"/>
       <c r="L246" s="8"/>
     </row>
@@ -15282,7 +15792,9 @@
       <c r="G247" s="3"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
-      <c r="J247" s="7"/>
+      <c r="J247" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K247" s="8"/>
       <c r="L247" s="8"/>
     </row>
@@ -15306,7 +15818,9 @@
       <c r="G248" s="3"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
-      <c r="J248" s="7"/>
+      <c r="J248" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K248" s="8"/>
       <c r="L248" s="8"/>
     </row>
@@ -15334,7 +15848,9 @@
         <v>966</v>
       </c>
       <c r="I249" s="4"/>
-      <c r="J249" s="7"/>
+      <c r="J249" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K249" s="8"/>
       <c r="L249" s="8"/>
     </row>
@@ -15358,7 +15874,9 @@
       <c r="G250" s="3"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
-      <c r="J250" s="7"/>
+      <c r="J250" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K250" s="8"/>
       <c r="L250" s="8"/>
     </row>
@@ -15382,7 +15900,9 @@
       <c r="G251" s="3"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
-      <c r="J251" s="7"/>
+      <c r="J251" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K251" s="8"/>
       <c r="L251" s="8"/>
     </row>
@@ -15406,7 +15926,9 @@
       <c r="G252" s="3"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
-      <c r="J252" s="7"/>
+      <c r="J252" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K252" s="8"/>
       <c r="L252" s="8"/>
     </row>
@@ -15430,7 +15952,9 @@
       <c r="G253" s="3"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
-      <c r="J253" s="7"/>
+      <c r="J253" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K253" s="8"/>
       <c r="L253" s="8"/>
     </row>
@@ -15454,7 +15978,9 @@
       <c r="G254" s="3"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
-      <c r="J254" s="7"/>
+      <c r="J254" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K254" s="8"/>
       <c r="L254" s="8"/>
     </row>
@@ -15478,7 +16004,9 @@
       <c r="G255" s="3"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
-      <c r="J255" s="7"/>
+      <c r="J255" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K255" s="8"/>
       <c r="L255" s="8"/>
     </row>
@@ -15502,7 +16030,9 @@
       <c r="G256" s="3"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
-      <c r="J256" s="7"/>
+      <c r="J256" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K256" s="8"/>
       <c r="L256" s="8"/>
     </row>
@@ -15526,7 +16056,9 @@
       <c r="G257" s="3"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
-      <c r="J257" s="7"/>
+      <c r="J257" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K257" s="8"/>
       <c r="L257" s="8"/>
     </row>
@@ -15550,7 +16082,9 @@
       <c r="G258" s="3"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
-      <c r="J258" s="7"/>
+      <c r="J258" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K258" s="8"/>
       <c r="L258" s="8"/>
     </row>
@@ -15574,7 +16108,9 @@
       <c r="G259" s="3"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
-      <c r="J259" s="7"/>
+      <c r="J259" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K259" s="8"/>
       <c r="L259" s="8"/>
     </row>
@@ -15598,7 +16134,9 @@
       <c r="G260" s="3"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
-      <c r="J260" s="7"/>
+      <c r="J260" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K260" s="8"/>
       <c r="L260" s="8"/>
     </row>
@@ -15622,7 +16160,9 @@
       <c r="G261" s="3"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
-      <c r="J261" s="7"/>
+      <c r="J261" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K261" s="8"/>
       <c r="L261" s="8"/>
     </row>
@@ -15646,7 +16186,9 @@
       <c r="G262" s="3"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
-      <c r="J262" s="7"/>
+      <c r="J262" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K262" s="8"/>
       <c r="L262" s="8"/>
     </row>
@@ -15670,7 +16212,9 @@
       <c r="G263" s="3"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
-      <c r="J263" s="7"/>
+      <c r="J263" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K263" s="8"/>
       <c r="L263" s="8"/>
     </row>
@@ -15694,7 +16238,9 @@
       <c r="G264" s="3"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
-      <c r="J264" s="7"/>
+      <c r="J264" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K264" s="8"/>
       <c r="L264" s="8"/>
     </row>
@@ -15718,7 +16264,9 @@
       <c r="G265" s="3"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
-      <c r="J265" s="7"/>
+      <c r="J265" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K265" s="8"/>
       <c r="L265" s="8"/>
     </row>
@@ -15742,7 +16290,9 @@
       <c r="G266" s="3"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
-      <c r="J266" s="7"/>
+      <c r="J266" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K266" s="8"/>
       <c r="L266" s="8"/>
     </row>
@@ -15766,7 +16316,9 @@
       <c r="G267" s="3"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
-      <c r="J267" s="7"/>
+      <c r="J267" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K267" s="8"/>
       <c r="L267" s="8"/>
     </row>
@@ -15790,7 +16342,9 @@
       <c r="G268" s="3"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
-      <c r="J268" s="7"/>
+      <c r="J268" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K268" s="8"/>
       <c r="L268" s="8"/>
     </row>
@@ -15814,7 +16368,9 @@
       <c r="G269" s="3"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
-      <c r="J269" s="7"/>
+      <c r="J269" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K269" s="8"/>
       <c r="L269" s="8"/>
     </row>
@@ -15838,7 +16394,9 @@
       <c r="G270" s="3"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
-      <c r="J270" s="7"/>
+      <c r="J270" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K270" s="8"/>
       <c r="L270" s="8"/>
     </row>
@@ -15862,7 +16420,9 @@
       <c r="G271" s="3"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
-      <c r="J271" s="7"/>
+      <c r="J271" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K271" s="8"/>
       <c r="L271" s="8"/>
     </row>
@@ -15890,7 +16450,9 @@
         <v>1035</v>
       </c>
       <c r="I272" s="4"/>
-      <c r="J272" s="7"/>
+      <c r="J272" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K272" s="8"/>
       <c r="L272" s="8"/>
     </row>
@@ -15914,7 +16476,9 @@
       <c r="G273" s="3"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
-      <c r="J273" s="7"/>
+      <c r="J273" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K273" s="8"/>
       <c r="L273" s="8"/>
     </row>
@@ -15938,7 +16502,9 @@
       <c r="G274" s="3"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
-      <c r="J274" s="7"/>
+      <c r="J274" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K274" s="8"/>
       <c r="L274" s="8"/>
     </row>
@@ -15962,7 +16528,9 @@
       <c r="G275" s="3"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
-      <c r="J275" s="7"/>
+      <c r="J275" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K275" s="8"/>
       <c r="L275" s="8"/>
     </row>
@@ -15986,7 +16554,9 @@
       <c r="G276" s="3"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
-      <c r="J276" s="7"/>
+      <c r="J276" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K276" s="8"/>
       <c r="L276" s="8"/>
     </row>
@@ -16010,7 +16580,9 @@
       <c r="G277" s="3"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
-      <c r="J277" s="7"/>
+      <c r="J277" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K277" s="8"/>
       <c r="L277" s="8"/>
     </row>
@@ -16034,7 +16606,9 @@
       <c r="G278" s="3"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
-      <c r="J278" s="7"/>
+      <c r="J278" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K278" s="8"/>
       <c r="L278" s="8"/>
     </row>
@@ -16058,7 +16632,9 @@
       <c r="G279" s="3"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
-      <c r="J279" s="7"/>
+      <c r="J279" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K279" s="8"/>
       <c r="L279" s="8"/>
     </row>
@@ -16082,7 +16658,9 @@
       <c r="G280" s="3"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
-      <c r="J280" s="7"/>
+      <c r="J280" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K280" s="8"/>
       <c r="L280" s="8"/>
     </row>
@@ -16106,7 +16684,9 @@
       <c r="G281" s="3"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
-      <c r="J281" s="7"/>
+      <c r="J281" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K281" s="8"/>
       <c r="L281" s="8"/>
     </row>
@@ -16130,7 +16710,9 @@
       <c r="G282" s="3"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
-      <c r="J282" s="7"/>
+      <c r="J282" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K282" s="8"/>
       <c r="L282" s="8"/>
     </row>
@@ -16154,7 +16736,9 @@
       <c r="G283" s="3"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
-      <c r="J283" s="7"/>
+      <c r="J283" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K283" s="8"/>
       <c r="L283" s="8"/>
     </row>
@@ -16178,7 +16762,9 @@
       <c r="G284" s="3"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
-      <c r="J284" s="7"/>
+      <c r="J284" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K284" s="8"/>
       <c r="L284" s="8"/>
     </row>
@@ -16202,7 +16788,9 @@
       <c r="G285" s="3"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
-      <c r="J285" s="7"/>
+      <c r="J285" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K285" s="8"/>
       <c r="L285" s="8"/>
     </row>
@@ -16226,7 +16814,9 @@
       <c r="G286" s="3"/>
       <c r="H286" s="4"/>
       <c r="I286" s="4"/>
-      <c r="J286" s="7"/>
+      <c r="J286" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K286" s="8"/>
       <c r="L286" s="8"/>
     </row>
@@ -16250,7 +16840,9 @@
       <c r="G287" s="3"/>
       <c r="H287" s="4"/>
       <c r="I287" s="4"/>
-      <c r="J287" s="7"/>
+      <c r="J287" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K287" s="8"/>
       <c r="L287" s="8"/>
     </row>
@@ -16274,7 +16866,9 @@
       <c r="G288" s="3"/>
       <c r="H288" s="4"/>
       <c r="I288" s="4"/>
-      <c r="J288" s="7"/>
+      <c r="J288" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K288" s="8"/>
       <c r="L288" s="8"/>
     </row>
@@ -16298,7 +16892,9 @@
       <c r="G289" s="3"/>
       <c r="H289" s="4"/>
       <c r="I289" s="4"/>
-      <c r="J289" s="7"/>
+      <c r="J289" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K289" s="8"/>
       <c r="L289" s="8"/>
     </row>
@@ -16322,7 +16918,9 @@
       <c r="G290" s="3"/>
       <c r="H290" s="4"/>
       <c r="I290" s="4"/>
-      <c r="J290" s="7"/>
+      <c r="J290" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K290" s="8"/>
       <c r="L290" s="8"/>
     </row>
@@ -16346,7 +16944,9 @@
       <c r="G291" s="3"/>
       <c r="H291" s="4"/>
       <c r="I291" s="4"/>
-      <c r="J291" s="7"/>
+      <c r="J291" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K291" s="8"/>
       <c r="L291" s="8"/>
     </row>
@@ -16370,7 +16970,9 @@
       <c r="G292" s="3"/>
       <c r="H292" s="4"/>
       <c r="I292" s="4"/>
-      <c r="J292" s="7"/>
+      <c r="J292" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K292" s="8"/>
       <c r="L292" s="8"/>
     </row>
@@ -16394,7 +16996,9 @@
       <c r="G293" s="3"/>
       <c r="H293" s="4"/>
       <c r="I293" s="4"/>
-      <c r="J293" s="7"/>
+      <c r="J293" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K293" s="8"/>
       <c r="L293" s="8"/>
     </row>
@@ -16418,7 +17022,9 @@
       <c r="G294" s="3"/>
       <c r="H294" s="4"/>
       <c r="I294" s="4"/>
-      <c r="J294" s="7"/>
+      <c r="J294" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K294" s="8"/>
       <c r="L294" s="8"/>
     </row>
@@ -16442,7 +17048,9 @@
       <c r="G295" s="3"/>
       <c r="H295" s="4"/>
       <c r="I295" s="4"/>
-      <c r="J295" s="7"/>
+      <c r="J295" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K295" s="8"/>
       <c r="L295" s="8"/>
     </row>
@@ -16466,7 +17074,9 @@
       <c r="G296" s="3"/>
       <c r="H296" s="4"/>
       <c r="I296" s="4"/>
-      <c r="J296" s="7"/>
+      <c r="J296" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K296" s="8"/>
       <c r="L296" s="8"/>
     </row>
@@ -16490,7 +17100,9 @@
       <c r="G297" s="3"/>
       <c r="H297" s="4"/>
       <c r="I297" s="4"/>
-      <c r="J297" s="7"/>
+      <c r="J297" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K297" s="8"/>
       <c r="L297" s="8"/>
     </row>
@@ -16514,7 +17126,9 @@
       <c r="G298" s="3"/>
       <c r="H298" s="4"/>
       <c r="I298" s="4"/>
-      <c r="J298" s="7"/>
+      <c r="J298" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K298" s="8"/>
       <c r="L298" s="8"/>
     </row>
@@ -16538,7 +17152,9 @@
       <c r="G299" s="3"/>
       <c r="H299" s="4"/>
       <c r="I299" s="4"/>
-      <c r="J299" s="7"/>
+      <c r="J299" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K299" s="8"/>
       <c r="L299" s="8"/>
     </row>
@@ -16562,7 +17178,9 @@
       <c r="G300" s="3"/>
       <c r="H300" s="4"/>
       <c r="I300" s="4"/>
-      <c r="J300" s="7"/>
+      <c r="J300" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K300" s="8"/>
       <c r="L300" s="8"/>
     </row>
@@ -16586,7 +17204,9 @@
       <c r="G301" s="3"/>
       <c r="H301" s="4"/>
       <c r="I301" s="4"/>
-      <c r="J301" s="7"/>
+      <c r="J301" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K301" s="8"/>
       <c r="L301" s="8"/>
     </row>
@@ -16610,7 +17230,9 @@
       <c r="G302" s="3"/>
       <c r="H302" s="4"/>
       <c r="I302" s="4"/>
-      <c r="J302" s="7"/>
+      <c r="J302" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K302" s="8"/>
       <c r="L302" s="8"/>
     </row>
@@ -16634,7 +17256,9 @@
       <c r="G303" s="3"/>
       <c r="H303" s="4"/>
       <c r="I303" s="4"/>
-      <c r="J303" s="7"/>
+      <c r="J303" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K303" s="8"/>
       <c r="L303" s="8"/>
     </row>
@@ -16658,7 +17282,9 @@
       <c r="G304" s="3"/>
       <c r="H304" s="4"/>
       <c r="I304" s="4"/>
-      <c r="J304" s="7"/>
+      <c r="J304" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K304" s="8"/>
       <c r="L304" s="8"/>
     </row>
@@ -16682,7 +17308,9 @@
       <c r="G305" s="3"/>
       <c r="H305" s="4"/>
       <c r="I305" s="4"/>
-      <c r="J305" s="7"/>
+      <c r="J305" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K305" s="8"/>
       <c r="L305" s="8"/>
     </row>
@@ -16706,7 +17334,9 @@
       <c r="G306" s="3"/>
       <c r="H306" s="4"/>
       <c r="I306" s="4"/>
-      <c r="J306" s="7"/>
+      <c r="J306" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K306" s="8"/>
       <c r="L306" s="8"/>
     </row>
@@ -16730,7 +17360,9 @@
       <c r="G307" s="3"/>
       <c r="H307" s="4"/>
       <c r="I307" s="4"/>
-      <c r="J307" s="7"/>
+      <c r="J307" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K307" s="8"/>
       <c r="L307" s="8"/>
     </row>
@@ -16754,7 +17386,9 @@
       <c r="G308" s="3"/>
       <c r="H308" s="4"/>
       <c r="I308" s="4"/>
-      <c r="J308" s="7"/>
+      <c r="J308" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K308" s="8"/>
       <c r="L308" s="8"/>
     </row>
@@ -16778,7 +17412,9 @@
       <c r="G309" s="3"/>
       <c r="H309" s="4"/>
       <c r="I309" s="4"/>
-      <c r="J309" s="7"/>
+      <c r="J309" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K309" s="8"/>
       <c r="L309" s="8"/>
     </row>
@@ -16802,7 +17438,9 @@
       <c r="G310" s="3"/>
       <c r="H310" s="4"/>
       <c r="I310" s="4"/>
-      <c r="J310" s="7"/>
+      <c r="J310" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K310" s="8"/>
       <c r="L310" s="8"/>
     </row>
@@ -16826,7 +17464,9 @@
       <c r="G311" s="3"/>
       <c r="H311" s="4"/>
       <c r="I311" s="4"/>
-      <c r="J311" s="7"/>
+      <c r="J311" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K311" s="8"/>
       <c r="L311" s="8"/>
     </row>
@@ -16850,7 +17490,9 @@
       <c r="G312" s="3"/>
       <c r="H312" s="4"/>
       <c r="I312" s="4"/>
-      <c r="J312" s="7"/>
+      <c r="J312" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K312" s="8"/>
       <c r="L312" s="8"/>
     </row>
@@ -16874,7 +17516,9 @@
       <c r="G313" s="3"/>
       <c r="H313" s="4"/>
       <c r="I313" s="4"/>
-      <c r="J313" s="7"/>
+      <c r="J313" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K313" s="8"/>
       <c r="L313" s="8"/>
     </row>
@@ -16898,7 +17542,9 @@
       <c r="G314" s="3"/>
       <c r="H314" s="4"/>
       <c r="I314" s="4"/>
-      <c r="J314" s="7"/>
+      <c r="J314" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K314" s="8"/>
       <c r="L314" s="8"/>
     </row>
@@ -16922,7 +17568,9 @@
       <c r="G315" s="3"/>
       <c r="H315" s="4"/>
       <c r="I315" s="4"/>
-      <c r="J315" s="7"/>
+      <c r="J315" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K315" s="8"/>
       <c r="L315" s="8"/>
     </row>
@@ -16946,7 +17594,9 @@
       <c r="G316" s="3"/>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
-      <c r="J316" s="7"/>
+      <c r="J316" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K316" s="8"/>
       <c r="L316" s="8"/>
     </row>
@@ -16970,7 +17620,9 @@
       <c r="G317" s="3"/>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
-      <c r="J317" s="7"/>
+      <c r="J317" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K317" s="8"/>
       <c r="L317" s="8"/>
     </row>
@@ -16994,7 +17646,9 @@
       <c r="G318" s="3"/>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
-      <c r="J318" s="7"/>
+      <c r="J318" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K318" s="8"/>
       <c r="L318" s="8"/>
     </row>
@@ -17018,7 +17672,9 @@
       <c r="G319" s="3"/>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
-      <c r="J319" s="7"/>
+      <c r="J319" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K319" s="8"/>
       <c r="L319" s="8"/>
     </row>
@@ -17042,7 +17698,9 @@
       <c r="G320" s="3"/>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
-      <c r="J320" s="7"/>
+      <c r="J320" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K320" s="8"/>
       <c r="L320" s="8"/>
     </row>
@@ -17066,7 +17724,9 @@
       <c r="G321" s="3"/>
       <c r="H321" s="4"/>
       <c r="I321" s="4"/>
-      <c r="J321" s="7"/>
+      <c r="J321" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K321" s="8"/>
       <c r="L321" s="8"/>
     </row>
@@ -17090,7 +17750,9 @@
       <c r="G322" s="3"/>
       <c r="H322" s="4"/>
       <c r="I322" s="4"/>
-      <c r="J322" s="7"/>
+      <c r="J322" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K322" s="8"/>
       <c r="L322" s="8"/>
     </row>
@@ -17114,7 +17776,9 @@
       <c r="G323" s="3"/>
       <c r="H323" s="4"/>
       <c r="I323" s="4"/>
-      <c r="J323" s="7"/>
+      <c r="J323" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K323" s="8"/>
       <c r="L323" s="8"/>
     </row>
@@ -17138,7 +17802,9 @@
       <c r="G324" s="3"/>
       <c r="H324" s="4"/>
       <c r="I324" s="4"/>
-      <c r="J324" s="7"/>
+      <c r="J324" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K324" s="8"/>
       <c r="L324" s="8"/>
     </row>
@@ -17162,7 +17828,9 @@
       <c r="G325" s="3"/>
       <c r="H325" s="4"/>
       <c r="I325" s="4"/>
-      <c r="J325" s="7"/>
+      <c r="J325" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K325" s="8"/>
       <c r="L325" s="8"/>
     </row>
@@ -17186,7 +17854,9 @@
       <c r="G326" s="3"/>
       <c r="H326" s="4"/>
       <c r="I326" s="4"/>
-      <c r="J326" s="7"/>
+      <c r="J326" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K326" s="8"/>
       <c r="L326" s="8"/>
     </row>
@@ -17212,7 +17882,9 @@
       <c r="I327" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J327" s="7"/>
+      <c r="J327" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K327" s="8"/>
       <c r="L327" s="8"/>
     </row>
@@ -17236,7 +17908,9 @@
       <c r="G328" s="3"/>
       <c r="H328" s="4"/>
       <c r="I328" s="4"/>
-      <c r="J328" s="7"/>
+      <c r="J328" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K328" s="8"/>
       <c r="L328" s="8"/>
     </row>
@@ -17260,7 +17934,9 @@
       <c r="G329" s="3"/>
       <c r="H329" s="4"/>
       <c r="I329" s="4"/>
-      <c r="J329" s="7"/>
+      <c r="J329" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K329" s="8"/>
       <c r="L329" s="8"/>
     </row>
@@ -17284,7 +17960,9 @@
       <c r="G330" s="3"/>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
-      <c r="J330" s="7"/>
+      <c r="J330" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K330" s="8"/>
       <c r="L330" s="8"/>
     </row>
@@ -17308,7 +17986,9 @@
       <c r="G331" s="3"/>
       <c r="H331" s="4"/>
       <c r="I331" s="4"/>
-      <c r="J331" s="7"/>
+      <c r="J331" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K331" s="8"/>
       <c r="L331" s="8"/>
     </row>
@@ -17332,7 +18012,9 @@
       <c r="G332" s="3"/>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
-      <c r="J332" s="7"/>
+      <c r="J332" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K332" s="8"/>
       <c r="L332" s="8"/>
     </row>
@@ -17356,7 +18038,9 @@
       <c r="G333" s="3"/>
       <c r="H333" s="4"/>
       <c r="I333" s="4"/>
-      <c r="J333" s="7"/>
+      <c r="J333" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K333" s="8"/>
       <c r="L333" s="8"/>
     </row>
@@ -17380,7 +18064,9 @@
       <c r="G334" s="3"/>
       <c r="H334" s="4"/>
       <c r="I334" s="4"/>
-      <c r="J334" s="7"/>
+      <c r="J334" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K334" s="8"/>
       <c r="L334" s="8"/>
     </row>
@@ -17404,7 +18090,9 @@
       <c r="G335" s="3"/>
       <c r="H335" s="4"/>
       <c r="I335" s="4"/>
-      <c r="J335" s="7"/>
+      <c r="J335" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K335" s="8"/>
       <c r="L335" s="8"/>
     </row>
@@ -17428,7 +18116,9 @@
       <c r="G336" s="3"/>
       <c r="H336" s="4"/>
       <c r="I336" s="4"/>
-      <c r="J336" s="7"/>
+      <c r="J336" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K336" s="8"/>
       <c r="L336" s="8"/>
     </row>
@@ -17458,7 +18148,9 @@
         <v>1235</v>
       </c>
       <c r="I337" s="4"/>
-      <c r="J337" s="7"/>
+      <c r="J337" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K337" s="8"/>
       <c r="L337" s="8"/>
     </row>
@@ -17488,7 +18180,9 @@
         <v>1240</v>
       </c>
       <c r="I338" s="4"/>
-      <c r="J338" s="7"/>
+      <c r="J338" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K338" s="8"/>
       <c r="L338" s="8"/>
     </row>
@@ -17516,7 +18210,9 @@
       <c r="I339" s="10" t="s">
         <v>1244</v>
       </c>
-      <c r="J339" s="7"/>
+      <c r="J339" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K339" s="8"/>
       <c r="L339" s="8"/>
     </row>
@@ -17546,7 +18242,9 @@
         <v>1235</v>
       </c>
       <c r="I340" s="4"/>
-      <c r="J340" s="7"/>
+      <c r="J340" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K340" s="8"/>
       <c r="L340" s="8"/>
     </row>
@@ -17576,7 +18274,9 @@
         <v>1253</v>
       </c>
       <c r="I341" s="4"/>
-      <c r="J341" s="7"/>
+      <c r="J341" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K341" s="8"/>
       <c r="L341" s="8"/>
     </row>
@@ -17606,7 +18306,9 @@
         <v>1258</v>
       </c>
       <c r="I342" s="4"/>
-      <c r="J342" s="7"/>
+      <c r="J342" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K342" s="8"/>
       <c r="L342" s="8"/>
     </row>
@@ -17636,7 +18338,9 @@
         <v>1263</v>
       </c>
       <c r="I343" s="4"/>
-      <c r="J343" s="7"/>
+      <c r="J343" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K343" s="8"/>
       <c r="L343" s="8"/>
     </row>
@@ -17666,7 +18370,9 @@
         <v>1268</v>
       </c>
       <c r="I344" s="4"/>
-      <c r="J344" s="7"/>
+      <c r="J344" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K344" s="8"/>
       <c r="L344" s="8"/>
     </row>
@@ -17692,7 +18398,9 @@
       <c r="G345" s="3"/>
       <c r="H345" s="4"/>
       <c r="I345" s="4"/>
-      <c r="J345" s="7"/>
+      <c r="J345" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K345" s="8"/>
       <c r="L345" s="8"/>
     </row>
@@ -17722,7 +18430,9 @@
         <v>1276</v>
       </c>
       <c r="I346" s="4"/>
-      <c r="J346" s="7"/>
+      <c r="J346" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K346" s="8"/>
       <c r="L346" s="8"/>
     </row>
@@ -17752,7 +18462,9 @@
         <v>1281</v>
       </c>
       <c r="I347" s="4"/>
-      <c r="J347" s="7"/>
+      <c r="J347" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K347" s="8"/>
       <c r="L347" s="8"/>
     </row>
@@ -17778,7 +18490,9 @@
       <c r="G348" s="3"/>
       <c r="H348" s="4"/>
       <c r="I348" s="4"/>
-      <c r="J348" s="7"/>
+      <c r="J348" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K348" s="8"/>
       <c r="L348" s="8"/>
     </row>
@@ -17806,7 +18520,9 @@
       <c r="I349" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J349" s="7"/>
+      <c r="J349" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K349" s="8"/>
       <c r="L349" s="8"/>
     </row>
@@ -17836,7 +18552,9 @@
         <v>1253</v>
       </c>
       <c r="I350" s="4"/>
-      <c r="J350" s="7"/>
+      <c r="J350" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K350" s="8"/>
       <c r="L350" s="8"/>
     </row>
@@ -17862,7 +18580,9 @@
       <c r="G351" s="3"/>
       <c r="H351" s="4"/>
       <c r="I351" s="4"/>
-      <c r="J351" s="7"/>
+      <c r="J351" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K351" s="8"/>
       <c r="L351" s="8"/>
     </row>
@@ -17890,7 +18610,9 @@
       <c r="I352" s="10" t="s">
         <v>1295</v>
       </c>
-      <c r="J352" s="7"/>
+      <c r="J352" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K352" s="8"/>
       <c r="L352" s="8"/>
     </row>
@@ -17916,7 +18638,9 @@
       <c r="G353" s="3"/>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
-      <c r="J353" s="7"/>
+      <c r="J353" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K353" s="8"/>
       <c r="L353" s="8"/>
     </row>
@@ -17942,7 +18666,9 @@
       <c r="G354" s="3"/>
       <c r="H354" s="4"/>
       <c r="I354" s="4"/>
-      <c r="J354" s="7"/>
+      <c r="J354" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K354" s="8"/>
       <c r="L354" s="8"/>
     </row>
@@ -17972,7 +18698,9 @@
         <v>1305</v>
       </c>
       <c r="I355" s="4"/>
-      <c r="J355" s="7"/>
+      <c r="J355" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K355" s="8"/>
       <c r="L355" s="8"/>
     </row>
@@ -17996,7 +18724,9 @@
       <c r="G356" s="3"/>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
-      <c r="J356" s="7"/>
+      <c r="J356" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K356" s="8"/>
       <c r="L356" s="8"/>
     </row>
@@ -18020,7 +18750,9 @@
       <c r="G357" s="3"/>
       <c r="H357" s="4"/>
       <c r="I357" s="4"/>
-      <c r="J357" s="7"/>
+      <c r="J357" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K357" s="8"/>
       <c r="L357" s="8"/>
     </row>
@@ -18044,7 +18776,9 @@
       <c r="G358" s="3"/>
       <c r="H358" s="4"/>
       <c r="I358" s="4"/>
-      <c r="J358" s="7"/>
+      <c r="J358" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K358" s="8"/>
       <c r="L358" s="8"/>
     </row>
@@ -18068,7 +18802,9 @@
       <c r="G359" s="3"/>
       <c r="H359" s="4"/>
       <c r="I359" s="4"/>
-      <c r="J359" s="7"/>
+      <c r="J359" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K359" s="8"/>
       <c r="L359" s="8"/>
     </row>
@@ -18096,7 +18832,9 @@
         <v>1318</v>
       </c>
       <c r="I360" s="4"/>
-      <c r="J360" s="7"/>
+      <c r="J360" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K360" s="8"/>
       <c r="L360" s="8"/>
     </row>
@@ -18120,7 +18858,9 @@
       <c r="G361" s="3"/>
       <c r="H361" s="4"/>
       <c r="I361" s="4"/>
-      <c r="J361" s="7"/>
+      <c r="J361" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K361" s="8"/>
       <c r="L361" s="8"/>
     </row>
@@ -18150,7 +18890,9 @@
         <v>1326</v>
       </c>
       <c r="I362" s="4"/>
-      <c r="J362" s="7"/>
+      <c r="J362" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K362" s="8"/>
       <c r="L362" s="8"/>
     </row>
@@ -18180,7 +18922,9 @@
       <c r="I363" s="10" t="s">
         <v>1331</v>
       </c>
-      <c r="J363" s="7"/>
+      <c r="J363" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K363" s="8"/>
       <c r="L363" s="8"/>
     </row>
@@ -18210,7 +18954,9 @@
         <v>1336</v>
       </c>
       <c r="I364" s="4"/>
-      <c r="J364" s="7"/>
+      <c r="J364" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K364" s="8"/>
       <c r="L364" s="8"/>
     </row>
@@ -18234,7 +18980,9 @@
       <c r="G365" s="3"/>
       <c r="H365" s="4"/>
       <c r="I365" s="4"/>
-      <c r="J365" s="7"/>
+      <c r="J365" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K365" s="8"/>
       <c r="L365" s="8"/>
     </row>
@@ -18258,7 +19006,9 @@
       <c r="G366" s="3"/>
       <c r="H366" s="4"/>
       <c r="I366" s="4"/>
-      <c r="J366" s="7"/>
+      <c r="J366" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K366" s="8"/>
       <c r="L366" s="8"/>
     </row>
@@ -18282,7 +19032,9 @@
       <c r="G367" s="3"/>
       <c r="H367" s="4"/>
       <c r="I367" s="4"/>
-      <c r="J367" s="7"/>
+      <c r="J367" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K367" s="8"/>
       <c r="L367" s="8"/>
     </row>
@@ -18306,7 +19058,9 @@
       <c r="G368" s="3"/>
       <c r="H368" s="4"/>
       <c r="I368" s="4"/>
-      <c r="J368" s="7"/>
+      <c r="J368" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K368" s="8"/>
       <c r="L368" s="8"/>
     </row>
@@ -18330,7 +19084,9 @@
       <c r="G369" s="3"/>
       <c r="H369" s="4"/>
       <c r="I369" s="4"/>
-      <c r="J369" s="7"/>
+      <c r="J369" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K369" s="8"/>
       <c r="L369" s="8"/>
     </row>
@@ -18356,7 +19112,9 @@
       <c r="G370" s="3"/>
       <c r="H370" s="4"/>
       <c r="I370" s="4"/>
-      <c r="J370" s="7"/>
+      <c r="J370" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K370" s="8"/>
       <c r="L370" s="8"/>
     </row>
@@ -18382,7 +19140,9 @@
       <c r="G371" s="3"/>
       <c r="H371" s="4"/>
       <c r="I371" s="4"/>
-      <c r="J371" s="7"/>
+      <c r="J371" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K371" s="8"/>
       <c r="L371" s="8"/>
     </row>
@@ -18408,7 +19168,9 @@
       <c r="G372" s="3"/>
       <c r="H372" s="4"/>
       <c r="I372" s="4"/>
-      <c r="J372" s="7"/>
+      <c r="J372" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K372" s="8"/>
       <c r="L372" s="8"/>
     </row>
@@ -18434,7 +19196,9 @@
       <c r="G373" s="3"/>
       <c r="H373" s="4"/>
       <c r="I373" s="4"/>
-      <c r="J373" s="7"/>
+      <c r="J373" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K373" s="8"/>
       <c r="L373" s="8"/>
     </row>
@@ -18458,7 +19222,9 @@
       <c r="G374" s="3"/>
       <c r="H374" s="4"/>
       <c r="I374" s="4"/>
-      <c r="J374" s="7"/>
+      <c r="J374" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K374" s="8"/>
       <c r="L374" s="8"/>
     </row>
@@ -18484,7 +19250,9 @@
       <c r="G375" s="3"/>
       <c r="H375" s="4"/>
       <c r="I375" s="4"/>
-      <c r="J375" s="7"/>
+      <c r="J375" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K375" s="8"/>
       <c r="L375" s="8"/>
     </row>
@@ -18512,7 +19280,9 @@
         <v>1368</v>
       </c>
       <c r="I376" s="4"/>
-      <c r="J376" s="7"/>
+      <c r="J376" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K376" s="8"/>
       <c r="L376" s="8"/>
     </row>
@@ -18536,7 +19306,9 @@
       <c r="G377" s="3"/>
       <c r="H377" s="4"/>
       <c r="I377" s="4"/>
-      <c r="J377" s="7"/>
+      <c r="J377" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K377" s="8"/>
       <c r="L377" s="8"/>
     </row>
@@ -18562,7 +19334,9 @@
       <c r="G378" s="3"/>
       <c r="H378" s="4"/>
       <c r="I378" s="4"/>
-      <c r="J378" s="7"/>
+      <c r="J378" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K378" s="8"/>
       <c r="L378" s="8"/>
     </row>
@@ -18592,7 +19366,9 @@
         <v>1379</v>
       </c>
       <c r="I379" s="4"/>
-      <c r="J379" s="7"/>
+      <c r="J379" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K379" s="8"/>
       <c r="L379" s="8"/>
     </row>
@@ -18622,7 +19398,9 @@
         <v>1384</v>
       </c>
       <c r="I380" s="4"/>
-      <c r="J380" s="7"/>
+      <c r="J380" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K380" s="8"/>
       <c r="L380" s="8"/>
     </row>
@@ -18652,7 +19430,9 @@
         <v>1384</v>
       </c>
       <c r="I381" s="4"/>
-      <c r="J381" s="7"/>
+      <c r="J381" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K381" s="8"/>
       <c r="L381" s="8"/>
     </row>
@@ -18680,7 +19460,9 @@
         <v>1393</v>
       </c>
       <c r="I382" s="4"/>
-      <c r="J382" s="7"/>
+      <c r="J382" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K382" s="8"/>
       <c r="L382" s="8"/>
     </row>
@@ -18704,7 +19486,9 @@
       <c r="G383" s="3"/>
       <c r="H383" s="4"/>
       <c r="I383" s="4"/>
-      <c r="J383" s="7"/>
+      <c r="J383" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K383" s="8"/>
       <c r="L383" s="8"/>
     </row>
@@ -18728,7 +19512,9 @@
       <c r="G384" s="3"/>
       <c r="H384" s="4"/>
       <c r="I384" s="4"/>
-      <c r="J384" s="7"/>
+      <c r="J384" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K384" s="8"/>
       <c r="L384" s="8"/>
     </row>
@@ -18758,7 +19544,9 @@
         <v>1404</v>
       </c>
       <c r="I385" s="4"/>
-      <c r="J385" s="7"/>
+      <c r="J385" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K385" s="8"/>
       <c r="L385" s="8"/>
     </row>
@@ -18784,7 +19572,9 @@
       <c r="G386" s="3"/>
       <c r="H386" s="4"/>
       <c r="I386" s="4"/>
-      <c r="J386" s="7"/>
+      <c r="J386" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K386" s="8"/>
       <c r="L386" s="8"/>
     </row>
@@ -18810,7 +19600,9 @@
       <c r="G387" s="3"/>
       <c r="H387" s="4"/>
       <c r="I387" s="4"/>
-      <c r="J387" s="7"/>
+      <c r="J387" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K387" s="8"/>
       <c r="L387" s="8"/>
     </row>
@@ -18834,7 +19626,9 @@
       <c r="G388" s="3"/>
       <c r="H388" s="4"/>
       <c r="I388" s="4"/>
-      <c r="J388" s="7"/>
+      <c r="J388" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K388" s="8"/>
       <c r="L388" s="8"/>
     </row>
@@ -18858,7 +19652,9 @@
       <c r="G389" s="3"/>
       <c r="H389" s="4"/>
       <c r="I389" s="4"/>
-      <c r="J389" s="7"/>
+      <c r="J389" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K389" s="8"/>
       <c r="L389" s="8"/>
     </row>
@@ -18884,7 +19680,9 @@
       <c r="G390" s="3"/>
       <c r="H390" s="4"/>
       <c r="I390" s="4"/>
-      <c r="J390" s="7"/>
+      <c r="J390" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K390" s="8"/>
       <c r="L390" s="8"/>
     </row>
@@ -18914,7 +19712,9 @@
         <v>1336</v>
       </c>
       <c r="I391" s="4"/>
-      <c r="J391" s="7"/>
+      <c r="J391" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K391" s="8"/>
       <c r="L391" s="8"/>
     </row>
@@ -18944,7 +19744,9 @@
         <v>1427</v>
       </c>
       <c r="I392" s="4"/>
-      <c r="J392" s="7"/>
+      <c r="J392" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K392" s="8"/>
       <c r="L392" s="8"/>
     </row>
@@ -18970,7 +19772,9 @@
       <c r="G393" s="3"/>
       <c r="H393" s="4"/>
       <c r="I393" s="4"/>
-      <c r="J393" s="7"/>
+      <c r="J393" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K393" s="8"/>
       <c r="L393" s="8"/>
     </row>
@@ -18996,7 +19800,9 @@
       <c r="G394" s="3"/>
       <c r="H394" s="4"/>
       <c r="I394" s="4"/>
-      <c r="J394" s="7"/>
+      <c r="J394" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K394" s="8"/>
       <c r="L394" s="8"/>
     </row>
@@ -19022,7 +19828,9 @@
       <c r="G395" s="3"/>
       <c r="H395" s="4"/>
       <c r="I395" s="4"/>
-      <c r="J395" s="7"/>
+      <c r="J395" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K395" s="8"/>
       <c r="L395" s="8"/>
     </row>
@@ -19048,7 +19856,9 @@
       <c r="G396" s="3"/>
       <c r="H396" s="4"/>
       <c r="I396" s="4"/>
-      <c r="J396" s="7"/>
+      <c r="J396" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K396" s="8"/>
       <c r="L396" s="8"/>
     </row>
@@ -19074,7 +19884,9 @@
       <c r="G397" s="3"/>
       <c r="H397" s="4"/>
       <c r="I397" s="4"/>
-      <c r="J397" s="7"/>
+      <c r="J397" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K397" s="8"/>
       <c r="L397" s="8"/>
     </row>
@@ -19104,7 +19916,9 @@
         <v>1446</v>
       </c>
       <c r="I398" s="4"/>
-      <c r="J398" s="7"/>
+      <c r="J398" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K398" s="8"/>
       <c r="L398" s="8"/>
     </row>
@@ -19128,7 +19942,9 @@
       <c r="G399" s="3"/>
       <c r="H399" s="4"/>
       <c r="I399" s="4"/>
-      <c r="J399" s="7"/>
+      <c r="J399" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K399" s="8"/>
       <c r="L399" s="8"/>
     </row>
@@ -19152,7 +19968,9 @@
       <c r="G400" s="3"/>
       <c r="H400" s="4"/>
       <c r="I400" s="4"/>
-      <c r="J400" s="7"/>
+      <c r="J400" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K400" s="8"/>
       <c r="L400" s="8"/>
     </row>
@@ -19176,7 +19994,9 @@
       <c r="G401" s="3"/>
       <c r="H401" s="4"/>
       <c r="I401" s="4"/>
-      <c r="J401" s="7"/>
+      <c r="J401" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K401" s="8"/>
       <c r="L401" s="8"/>
     </row>
@@ -19202,7 +20022,9 @@
       <c r="G402" s="3"/>
       <c r="H402" s="4"/>
       <c r="I402" s="4"/>
-      <c r="J402" s="7"/>
+      <c r="J402" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K402" s="8"/>
       <c r="L402" s="8"/>
     </row>
@@ -19232,7 +20054,9 @@
         <v>1462</v>
       </c>
       <c r="I403" s="4"/>
-      <c r="J403" s="7"/>
+      <c r="J403" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K403" s="8"/>
       <c r="L403" s="8"/>
     </row>
@@ -19262,7 +20086,9 @@
         <v>1467</v>
       </c>
       <c r="I404" s="4"/>
-      <c r="J404" s="7"/>
+      <c r="J404" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K404" s="8"/>
       <c r="L404" s="8"/>
     </row>
@@ -19292,7 +20118,9 @@
         <v>830</v>
       </c>
       <c r="I405" s="4"/>
-      <c r="J405" s="7"/>
+      <c r="J405" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K405" s="8"/>
       <c r="L405" s="8"/>
     </row>
@@ -19322,7 +20150,9 @@
         <v>830</v>
       </c>
       <c r="I406" s="4"/>
-      <c r="J406" s="7"/>
+      <c r="J406" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K406" s="8"/>
       <c r="L406" s="8"/>
     </row>
@@ -19348,7 +20178,9 @@
       <c r="I407" s="10" t="s">
         <v>1479</v>
       </c>
-      <c r="J407" s="7"/>
+      <c r="J407" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K407" s="8"/>
       <c r="L407" s="8"/>
     </row>
@@ -19372,7 +20204,9 @@
       <c r="G408" s="3"/>
       <c r="H408" s="4"/>
       <c r="I408" s="4"/>
-      <c r="J408" s="7"/>
+      <c r="J408" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K408" s="8"/>
       <c r="L408" s="8"/>
     </row>
@@ -19398,7 +20232,9 @@
       <c r="G409" s="3"/>
       <c r="H409" s="4"/>
       <c r="I409" s="4"/>
-      <c r="J409" s="7"/>
+      <c r="J409" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K409" s="8"/>
       <c r="L409" s="8"/>
     </row>
@@ -19428,7 +20264,9 @@
         <v>1490</v>
       </c>
       <c r="I410" s="4"/>
-      <c r="J410" s="7"/>
+      <c r="J410" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K410" s="8"/>
       <c r="L410" s="8"/>
     </row>
@@ -19452,7 +20290,9 @@
       <c r="G411" s="3"/>
       <c r="H411" s="4"/>
       <c r="I411" s="4"/>
-      <c r="J411" s="7"/>
+      <c r="J411" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K411" s="8"/>
       <c r="L411" s="8"/>
     </row>
@@ -19476,7 +20316,9 @@
       <c r="G412" s="3"/>
       <c r="H412" s="4"/>
       <c r="I412" s="4"/>
-      <c r="J412" s="7"/>
+      <c r="J412" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K412" s="8"/>
       <c r="L412" s="8"/>
     </row>
@@ -19506,7 +20348,9 @@
         <v>1498</v>
       </c>
       <c r="I413" s="4"/>
-      <c r="J413" s="7"/>
+      <c r="J413" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K413" s="8"/>
       <c r="L413" s="8"/>
     </row>
@@ -19532,7 +20376,9 @@
       <c r="G414" s="3"/>
       <c r="H414" s="4"/>
       <c r="I414" s="4"/>
-      <c r="J414" s="7"/>
+      <c r="J414" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K414" s="8"/>
       <c r="L414" s="8"/>
     </row>
@@ -19558,7 +20404,9 @@
       <c r="G415" s="3"/>
       <c r="H415" s="4"/>
       <c r="I415" s="4"/>
-      <c r="J415" s="7"/>
+      <c r="J415" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K415" s="8"/>
       <c r="L415" s="8"/>
     </row>
@@ -19582,7 +20430,9 @@
       <c r="G416" s="3"/>
       <c r="H416" s="4"/>
       <c r="I416" s="4"/>
-      <c r="J416" s="7"/>
+      <c r="J416" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K416" s="8"/>
       <c r="L416" s="8"/>
     </row>
@@ -19612,7 +20462,9 @@
         <v>1512</v>
       </c>
       <c r="I417" s="4"/>
-      <c r="J417" s="7"/>
+      <c r="J417" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K417" s="8"/>
       <c r="L417" s="8"/>
     </row>
@@ -19638,7 +20490,9 @@
       <c r="G418" s="3"/>
       <c r="H418" s="4"/>
       <c r="I418" s="4"/>
-      <c r="J418" s="7"/>
+      <c r="J418" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K418" s="8"/>
       <c r="L418" s="8"/>
     </row>
@@ -19668,7 +20522,9 @@
         <v>1520</v>
       </c>
       <c r="I419" s="4"/>
-      <c r="J419" s="7"/>
+      <c r="J419" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K419" s="8"/>
       <c r="L419" s="8"/>
     </row>
@@ -19698,7 +20554,9 @@
         <v>1525</v>
       </c>
       <c r="I420" s="4"/>
-      <c r="J420" s="7"/>
+      <c r="J420" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K420" s="8"/>
       <c r="L420" s="8"/>
     </row>
@@ -19722,7 +20580,9 @@
       <c r="G421" s="3"/>
       <c r="H421" s="4"/>
       <c r="I421" s="4"/>
-      <c r="J421" s="7"/>
+      <c r="J421" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K421" s="8"/>
       <c r="L421" s="8"/>
     </row>
@@ -19746,7 +20606,9 @@
       <c r="G422" s="3"/>
       <c r="H422" s="4"/>
       <c r="I422" s="4"/>
-      <c r="J422" s="7"/>
+      <c r="J422" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K422" s="8"/>
       <c r="L422" s="8"/>
     </row>
@@ -19770,7 +20632,9 @@
       <c r="G423" s="3"/>
       <c r="H423" s="4"/>
       <c r="I423" s="4"/>
-      <c r="J423" s="7"/>
+      <c r="J423" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K423" s="8"/>
       <c r="L423" s="8"/>
     </row>
@@ -19794,7 +20658,9 @@
       <c r="G424" s="3"/>
       <c r="H424" s="4"/>
       <c r="I424" s="4"/>
-      <c r="J424" s="7"/>
+      <c r="J424" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K424" s="8"/>
       <c r="L424" s="8"/>
     </row>
@@ -19824,7 +20690,9 @@
         <v>1446</v>
       </c>
       <c r="I425" s="4"/>
-      <c r="J425" s="7"/>
+      <c r="J425" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K425" s="8"/>
       <c r="L425" s="8"/>
     </row>
@@ -19850,7 +20718,9 @@
       <c r="G426" s="3"/>
       <c r="H426" s="4"/>
       <c r="I426" s="4"/>
-      <c r="J426" s="7"/>
+      <c r="J426" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K426" s="8"/>
       <c r="L426" s="8"/>
     </row>
@@ -19880,7 +20750,9 @@
         <v>1547</v>
       </c>
       <c r="I427" s="4"/>
-      <c r="J427" s="7"/>
+      <c r="J427" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K427" s="8"/>
       <c r="L427" s="8"/>
     </row>
@@ -19910,7 +20782,9 @@
         <v>1552</v>
       </c>
       <c r="I428" s="4"/>
-      <c r="J428" s="7"/>
+      <c r="J428" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K428" s="8"/>
       <c r="L428" s="8"/>
     </row>
@@ -19936,7 +20810,9 @@
       <c r="I429" s="10" t="s">
         <v>1556</v>
       </c>
-      <c r="J429" s="7"/>
+      <c r="J429" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K429" s="8"/>
       <c r="L429" s="8"/>
     </row>
@@ -19960,7 +20836,9 @@
       <c r="G430" s="3"/>
       <c r="H430" s="4"/>
       <c r="I430" s="4"/>
-      <c r="J430" s="7"/>
+      <c r="J430" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K430" s="8"/>
       <c r="L430" s="8"/>
     </row>
@@ -19986,7 +20864,9 @@
       <c r="G431" s="3"/>
       <c r="H431" s="4"/>
       <c r="I431" s="4"/>
-      <c r="J431" s="7"/>
+      <c r="J431" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K431" s="8"/>
       <c r="L431" s="8"/>
     </row>
@@ -20016,7 +20896,9 @@
         <v>1567</v>
       </c>
       <c r="I432" s="4"/>
-      <c r="J432" s="7"/>
+      <c r="J432" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K432" s="8"/>
       <c r="L432" s="8"/>
     </row>
@@ -20046,7 +20928,9 @@
         <v>1572</v>
       </c>
       <c r="I433" s="4"/>
-      <c r="J433" s="7"/>
+      <c r="J433" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K433" s="8"/>
       <c r="L433" s="8"/>
     </row>
@@ -20072,7 +20956,9 @@
       <c r="G434" s="3"/>
       <c r="H434" s="4"/>
       <c r="I434" s="4"/>
-      <c r="J434" s="7"/>
+      <c r="J434" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K434" s="8"/>
       <c r="L434" s="8"/>
     </row>
@@ -20098,7 +20984,9 @@
       <c r="G435" s="3"/>
       <c r="H435" s="4"/>
       <c r="I435" s="4"/>
-      <c r="J435" s="7"/>
+      <c r="J435" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K435" s="8"/>
       <c r="L435" s="8"/>
     </row>
@@ -20122,7 +21010,9 @@
       <c r="G436" s="3"/>
       <c r="H436" s="4"/>
       <c r="I436" s="4"/>
-      <c r="J436" s="7"/>
+      <c r="J436" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K436" s="8"/>
       <c r="L436" s="8"/>
     </row>
@@ -20152,7 +21042,9 @@
         <v>1585</v>
       </c>
       <c r="I437" s="4"/>
-      <c r="J437" s="7"/>
+      <c r="J437" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K437" s="8"/>
       <c r="L437" s="8"/>
     </row>
@@ -20182,7 +21074,9 @@
         <v>1590</v>
       </c>
       <c r="I438" s="4"/>
-      <c r="J438" s="7"/>
+      <c r="J438" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K438" s="8"/>
       <c r="L438" s="8"/>
     </row>
@@ -20208,7 +21102,9 @@
       <c r="G439" s="3"/>
       <c r="H439" s="4"/>
       <c r="I439" s="4"/>
-      <c r="J439" s="7"/>
+      <c r="J439" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K439" s="8"/>
       <c r="L439" s="8"/>
     </row>
@@ -20234,7 +21130,9 @@
       <c r="G440" s="3"/>
       <c r="H440" s="4"/>
       <c r="I440" s="4"/>
-      <c r="J440" s="7"/>
+      <c r="J440" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K440" s="8"/>
       <c r="L440" s="8"/>
     </row>
@@ -20260,7 +21158,9 @@
       <c r="G441" s="3"/>
       <c r="H441" s="4"/>
       <c r="I441" s="4"/>
-      <c r="J441" s="7"/>
+      <c r="J441" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K441" s="8"/>
       <c r="L441" s="8"/>
     </row>
@@ -20286,7 +21186,9 @@
       <c r="G442" s="3"/>
       <c r="H442" s="4"/>
       <c r="I442" s="4"/>
-      <c r="J442" s="7"/>
+      <c r="J442" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K442" s="8"/>
       <c r="L442" s="8"/>
     </row>
@@ -20312,7 +21214,9 @@
       <c r="G443" s="3"/>
       <c r="H443" s="4"/>
       <c r="I443" s="4"/>
-      <c r="J443" s="7"/>
+      <c r="J443" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K443" s="8"/>
       <c r="L443" s="8"/>
     </row>
@@ -20338,7 +21242,9 @@
       <c r="G444" s="3"/>
       <c r="H444" s="4"/>
       <c r="I444" s="4"/>
-      <c r="J444" s="7"/>
+      <c r="J444" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K444" s="8"/>
       <c r="L444" s="8"/>
     </row>
@@ -20364,7 +21270,9 @@
       <c r="G445" s="3"/>
       <c r="H445" s="4"/>
       <c r="I445" s="4"/>
-      <c r="J445" s="7"/>
+      <c r="J445" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K445" s="8"/>
       <c r="L445" s="8"/>
     </row>
@@ -20394,7 +21302,9 @@
         <v>1615</v>
       </c>
       <c r="I446" s="4"/>
-      <c r="J446" s="7"/>
+      <c r="J446" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K446" s="8"/>
       <c r="L446" s="8"/>
     </row>
@@ -20420,7 +21330,9 @@
       <c r="G447" s="3"/>
       <c r="H447" s="4"/>
       <c r="I447" s="4"/>
-      <c r="J447" s="7"/>
+      <c r="J447" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K447" s="8"/>
       <c r="L447" s="8"/>
     </row>
@@ -20444,7 +21356,9 @@
       <c r="G448" s="3"/>
       <c r="H448" s="4"/>
       <c r="I448" s="4"/>
-      <c r="J448" s="7"/>
+      <c r="J448" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K448" s="8"/>
       <c r="L448" s="8"/>
     </row>
@@ -20470,7 +21384,9 @@
       <c r="G449" s="3"/>
       <c r="H449" s="4"/>
       <c r="I449" s="4"/>
-      <c r="J449" s="7"/>
+      <c r="J449" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K449" s="8"/>
       <c r="L449" s="8"/>
     </row>
@@ -20498,7 +21414,9 @@
         <v>1628</v>
       </c>
       <c r="I450" s="4"/>
-      <c r="J450" s="7"/>
+      <c r="J450" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K450" s="8"/>
       <c r="L450" s="8"/>
     </row>
@@ -20528,7 +21446,9 @@
         <v>1633</v>
       </c>
       <c r="I451" s="4"/>
-      <c r="J451" s="7"/>
+      <c r="J451" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K451" s="8"/>
       <c r="L451" s="8"/>
     </row>
@@ -20558,7 +21478,9 @@
         <v>1638</v>
       </c>
       <c r="I452" s="4"/>
-      <c r="J452" s="7"/>
+      <c r="J452" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K452" s="8"/>
       <c r="L452" s="8"/>
     </row>
@@ -20586,7 +21508,9 @@
         <v>1642</v>
       </c>
       <c r="I453" s="4"/>
-      <c r="J453" s="7"/>
+      <c r="J453" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K453" s="8"/>
       <c r="L453" s="8"/>
     </row>
@@ -20610,7 +21534,9 @@
       <c r="G454" s="3"/>
       <c r="H454" s="4"/>
       <c r="I454" s="4"/>
-      <c r="J454" s="7"/>
+      <c r="J454" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K454" s="8"/>
       <c r="L454" s="8"/>
     </row>
@@ -20636,7 +21562,9 @@
       <c r="G455" s="3"/>
       <c r="H455" s="4"/>
       <c r="I455" s="4"/>
-      <c r="J455" s="7"/>
+      <c r="J455" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K455" s="8"/>
       <c r="L455" s="8"/>
     </row>
@@ -20662,7 +21590,9 @@
       <c r="G456" s="3"/>
       <c r="H456" s="4"/>
       <c r="I456" s="4"/>
-      <c r="J456" s="7"/>
+      <c r="J456" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K456" s="8"/>
       <c r="L456" s="8"/>
     </row>
@@ -20688,7 +21618,9 @@
       <c r="G457" s="3"/>
       <c r="H457" s="4"/>
       <c r="I457" s="4"/>
-      <c r="J457" s="7"/>
+      <c r="J457" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K457" s="8"/>
       <c r="L457" s="8"/>
     </row>
@@ -20718,7 +21650,9 @@
         <v>1658</v>
       </c>
       <c r="I458" s="4"/>
-      <c r="J458" s="7"/>
+      <c r="J458" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K458" s="8"/>
       <c r="L458" s="8"/>
     </row>
@@ -20744,7 +21678,9 @@
       <c r="G459" s="3"/>
       <c r="H459" s="4"/>
       <c r="I459" s="4"/>
-      <c r="J459" s="7"/>
+      <c r="J459" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K459" s="8"/>
       <c r="L459" s="8"/>
     </row>
@@ -20770,7 +21706,9 @@
       <c r="G460" s="3"/>
       <c r="H460" s="4"/>
       <c r="I460" s="4"/>
-      <c r="J460" s="7"/>
+      <c r="J460" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K460" s="8"/>
       <c r="L460" s="8"/>
     </row>
@@ -20794,7 +21732,9 @@
       <c r="G461" s="3"/>
       <c r="H461" s="4"/>
       <c r="I461" s="4"/>
-      <c r="J461" s="7"/>
+      <c r="J461" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K461" s="8"/>
       <c r="L461" s="8"/>
     </row>
@@ -20818,7 +21758,9 @@
       <c r="G462" s="3"/>
       <c r="H462" s="4"/>
       <c r="I462" s="4"/>
-      <c r="J462" s="7"/>
+      <c r="J462" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K462" s="8"/>
       <c r="L462" s="8"/>
     </row>
@@ -20842,7 +21784,9 @@
       <c r="G463" s="3"/>
       <c r="H463" s="4"/>
       <c r="I463" s="4"/>
-      <c r="J463" s="7"/>
+      <c r="J463" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K463" s="8"/>
       <c r="L463" s="8"/>
     </row>
@@ -20866,7 +21810,9 @@
       <c r="G464" s="3"/>
       <c r="H464" s="4"/>
       <c r="I464" s="4"/>
-      <c r="J464" s="7"/>
+      <c r="J464" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K464" s="8"/>
       <c r="L464" s="8"/>
     </row>
@@ -20890,7 +21836,9 @@
       <c r="G465" s="3"/>
       <c r="H465" s="4"/>
       <c r="I465" s="4"/>
-      <c r="J465" s="7"/>
+      <c r="J465" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K465" s="8"/>
       <c r="L465" s="8"/>
     </row>
@@ -20914,7 +21862,9 @@
       <c r="G466" s="3"/>
       <c r="H466" s="4"/>
       <c r="I466" s="4"/>
-      <c r="J466" s="7"/>
+      <c r="J466" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K466" s="8"/>
       <c r="L466" s="8"/>
     </row>
@@ -20938,7 +21888,9 @@
       <c r="G467" s="3"/>
       <c r="H467" s="4"/>
       <c r="I467" s="4"/>
-      <c r="J467" s="7"/>
+      <c r="J467" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K467" s="8"/>
       <c r="L467" s="8"/>
     </row>
@@ -20962,7 +21914,9 @@
       <c r="G468" s="3"/>
       <c r="H468" s="4"/>
       <c r="I468" s="4"/>
-      <c r="J468" s="7"/>
+      <c r="J468" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K468" s="8"/>
       <c r="L468" s="8"/>
     </row>
@@ -20986,7 +21940,9 @@
       <c r="G469" s="3"/>
       <c r="H469" s="4"/>
       <c r="I469" s="4"/>
-      <c r="J469" s="7"/>
+      <c r="J469" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K469" s="8"/>
       <c r="L469" s="8"/>
     </row>
@@ -21010,7 +21966,9 @@
       <c r="G470" s="3"/>
       <c r="H470" s="4"/>
       <c r="I470" s="4"/>
-      <c r="J470" s="7"/>
+      <c r="J470" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K470" s="8"/>
       <c r="L470" s="8"/>
     </row>
@@ -21036,7 +21994,9 @@
       <c r="G471" s="3"/>
       <c r="H471" s="4"/>
       <c r="I471" s="4"/>
-      <c r="J471" s="7"/>
+      <c r="J471" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K471" s="8"/>
       <c r="L471" s="8"/>
     </row>
@@ -21060,7 +22020,9 @@
       <c r="G472" s="3"/>
       <c r="H472" s="4"/>
       <c r="I472" s="4"/>
-      <c r="J472" s="7"/>
+      <c r="J472" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K472" s="8"/>
       <c r="L472" s="8"/>
     </row>
@@ -21086,7 +22048,9 @@
       <c r="G473" s="3"/>
       <c r="H473" s="4"/>
       <c r="I473" s="4"/>
-      <c r="J473" s="7"/>
+      <c r="J473" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K473" s="8"/>
       <c r="L473" s="8"/>
     </row>
@@ -21112,7 +22076,9 @@
       <c r="G474" s="3"/>
       <c r="H474" s="4"/>
       <c r="I474" s="4"/>
-      <c r="J474" s="7"/>
+      <c r="J474" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K474" s="8"/>
       <c r="L474" s="8"/>
     </row>
@@ -21142,7 +22108,9 @@
         <v>1707</v>
       </c>
       <c r="I475" s="4"/>
-      <c r="J475" s="7"/>
+      <c r="J475" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K475" s="8"/>
       <c r="L475" s="8"/>
     </row>
@@ -21168,7 +22136,9 @@
       <c r="G476" s="3"/>
       <c r="H476" s="4"/>
       <c r="I476" s="4"/>
-      <c r="J476" s="7"/>
+      <c r="J476" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K476" s="8"/>
       <c r="L476" s="8"/>
     </row>
@@ -21194,7 +22164,9 @@
       <c r="G477" s="3"/>
       <c r="H477" s="4"/>
       <c r="I477" s="4"/>
-      <c r="J477" s="7"/>
+      <c r="J477" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K477" s="8"/>
       <c r="L477" s="8"/>
     </row>
@@ -21220,7 +22192,9 @@
       <c r="G478" s="3"/>
       <c r="H478" s="4"/>
       <c r="I478" s="4"/>
-      <c r="J478" s="7"/>
+      <c r="J478" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K478" s="8"/>
       <c r="L478" s="8"/>
     </row>
@@ -21244,7 +22218,9 @@
       <c r="G479" s="3"/>
       <c r="H479" s="4"/>
       <c r="I479" s="4"/>
-      <c r="J479" s="7"/>
+      <c r="J479" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K479" s="8"/>
       <c r="L479" s="8"/>
     </row>
@@ -21270,7 +22246,9 @@
       <c r="G480" s="3"/>
       <c r="H480" s="4"/>
       <c r="I480" s="4"/>
-      <c r="J480" s="7"/>
+      <c r="J480" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K480" s="8"/>
       <c r="L480" s="8"/>
     </row>
@@ -21300,7 +22278,9 @@
         <v>1722</v>
       </c>
       <c r="I481" s="4"/>
-      <c r="J481" s="7"/>
+      <c r="J481" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K481" s="8"/>
       <c r="L481" s="8"/>
     </row>
@@ -21326,7 +22306,9 @@
       <c r="G482" s="3"/>
       <c r="H482" s="4"/>
       <c r="I482" s="4"/>
-      <c r="J482" s="7"/>
+      <c r="J482" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K482" s="8"/>
       <c r="L482" s="8"/>
     </row>
@@ -21352,7 +22334,9 @@
       <c r="G483" s="3"/>
       <c r="H483" s="4"/>
       <c r="I483" s="4"/>
-      <c r="J483" s="7"/>
+      <c r="J483" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K483" s="8"/>
       <c r="L483" s="8"/>
     </row>
@@ -21378,7 +22362,9 @@
       <c r="G484" s="3"/>
       <c r="H484" s="4"/>
       <c r="I484" s="4"/>
-      <c r="J484" s="7"/>
+      <c r="J484" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K484" s="8"/>
       <c r="L484" s="8"/>
     </row>
@@ -21404,7 +22390,9 @@
       <c r="G485" s="3"/>
       <c r="H485" s="4"/>
       <c r="I485" s="4"/>
-      <c r="J485" s="7"/>
+      <c r="J485" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K485" s="8"/>
       <c r="L485" s="8"/>
     </row>
@@ -21434,7 +22422,9 @@
         <v>1738</v>
       </c>
       <c r="I486" s="4"/>
-      <c r="J486" s="7"/>
+      <c r="J486" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K486" s="8"/>
       <c r="L486" s="8"/>
     </row>
@@ -21464,7 +22454,9 @@
         <v>830</v>
       </c>
       <c r="I487" s="4"/>
-      <c r="J487" s="7"/>
+      <c r="J487" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K487" s="8"/>
       <c r="L487" s="8"/>
     </row>
@@ -21496,7 +22488,9 @@
       <c r="I488" s="10" t="s">
         <v>1748</v>
       </c>
-      <c r="J488" s="7"/>
+      <c r="J488" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K488" s="8"/>
       <c r="L488" s="8"/>
     </row>
@@ -21526,7 +22520,9 @@
         <v>1753</v>
       </c>
       <c r="I489" s="4"/>
-      <c r="J489" s="7"/>
+      <c r="J489" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K489" s="8"/>
       <c r="L489" s="8"/>
     </row>
@@ -21552,7 +22548,9 @@
       <c r="G490" s="3"/>
       <c r="H490" s="4"/>
       <c r="I490" s="4"/>
-      <c r="J490" s="7"/>
+      <c r="J490" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K490" s="8"/>
       <c r="L490" s="8"/>
     </row>
@@ -21578,7 +22576,9 @@
       <c r="G491" s="3"/>
       <c r="H491" s="4"/>
       <c r="I491" s="4"/>
-      <c r="J491" s="7"/>
+      <c r="J491" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K491" s="8"/>
       <c r="L491" s="8"/>
     </row>
@@ -21604,7 +22604,9 @@
       <c r="G492" s="3"/>
       <c r="H492" s="4"/>
       <c r="I492" s="4"/>
-      <c r="J492" s="7"/>
+      <c r="J492" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K492" s="8"/>
       <c r="L492" s="8"/>
     </row>
@@ -21630,7 +22632,9 @@
       <c r="G493" s="3"/>
       <c r="H493" s="4"/>
       <c r="I493" s="4"/>
-      <c r="J493" s="7"/>
+      <c r="J493" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K493" s="8"/>
       <c r="L493" s="8"/>
     </row>
@@ -21654,7 +22658,9 @@
       <c r="G494" s="3"/>
       <c r="H494" s="4"/>
       <c r="I494" s="4"/>
-      <c r="J494" s="7"/>
+      <c r="J494" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K494" s="8"/>
       <c r="L494" s="8"/>
     </row>
@@ -21678,7 +22684,9 @@
       <c r="G495" s="3"/>
       <c r="H495" s="4"/>
       <c r="I495" s="4"/>
-      <c r="J495" s="7"/>
+      <c r="J495" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K495" s="8"/>
       <c r="L495" s="8"/>
     </row>
@@ -21702,7 +22710,9 @@
       <c r="G496" s="3"/>
       <c r="H496" s="4"/>
       <c r="I496" s="4"/>
-      <c r="J496" s="7"/>
+      <c r="J496" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K496" s="8"/>
       <c r="L496" s="8"/>
     </row>
@@ -21726,7 +22736,9 @@
       <c r="G497" s="3"/>
       <c r="H497" s="4"/>
       <c r="I497" s="4"/>
-      <c r="J497" s="7"/>
+      <c r="J497" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K497" s="8"/>
       <c r="L497" s="8"/>
     </row>
@@ -21750,7 +22762,9 @@
       <c r="G498" s="3"/>
       <c r="H498" s="4"/>
       <c r="I498" s="4"/>
-      <c r="J498" s="7"/>
+      <c r="J498" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K498" s="8"/>
       <c r="L498" s="8"/>
     </row>
@@ -21774,7 +22788,9 @@
       <c r="G499" s="3"/>
       <c r="H499" s="4"/>
       <c r="I499" s="4"/>
-      <c r="J499" s="7"/>
+      <c r="J499" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K499" s="8"/>
       <c r="L499" s="8"/>
     </row>
@@ -21802,7 +22818,9 @@
         <v>1783</v>
       </c>
       <c r="I500" s="4"/>
-      <c r="J500" s="7"/>
+      <c r="J500" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K500" s="8"/>
       <c r="L500" s="8"/>
     </row>
@@ -21828,7 +22846,9 @@
       <c r="G501" s="3"/>
       <c r="H501" s="4"/>
       <c r="I501" s="4"/>
-      <c r="J501" s="7"/>
+      <c r="J501" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K501" s="8"/>
       <c r="L501" s="8"/>
     </row>
@@ -21854,7 +22874,9 @@
       <c r="G502" s="3"/>
       <c r="H502" s="4"/>
       <c r="I502" s="4"/>
-      <c r="J502" s="7"/>
+      <c r="J502" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K502" s="8"/>
       <c r="L502" s="8"/>
     </row>
@@ -21880,7 +22902,9 @@
       <c r="G503" s="3"/>
       <c r="H503" s="4"/>
       <c r="I503" s="4"/>
-      <c r="J503" s="7"/>
+      <c r="J503" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K503" s="8"/>
       <c r="L503" s="8"/>
     </row>
@@ -21906,7 +22930,9 @@
       <c r="G504" s="3"/>
       <c r="H504" s="4"/>
       <c r="I504" s="4"/>
-      <c r="J504" s="7"/>
+      <c r="J504" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K504" s="8"/>
       <c r="L504" s="8"/>
     </row>
@@ -21932,7 +22958,9 @@
       <c r="G505" s="3"/>
       <c r="H505" s="4"/>
       <c r="I505" s="4"/>
-      <c r="J505" s="7"/>
+      <c r="J505" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K505" s="8"/>
       <c r="L505" s="8"/>
     </row>
@@ -21958,7 +22986,9 @@
       <c r="G506" s="3"/>
       <c r="H506" s="4"/>
       <c r="I506" s="4"/>
-      <c r="J506" s="7"/>
+      <c r="J506" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K506" s="8"/>
       <c r="L506" s="8"/>
     </row>
@@ -21984,7 +23014,9 @@
       <c r="G507" s="3"/>
       <c r="H507" s="4"/>
       <c r="I507" s="4"/>
-      <c r="J507" s="7"/>
+      <c r="J507" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K507" s="8"/>
       <c r="L507" s="8"/>
     </row>
@@ -22010,7 +23042,9 @@
       <c r="G508" s="3"/>
       <c r="H508" s="4"/>
       <c r="I508" s="4"/>
-      <c r="J508" s="7"/>
+      <c r="J508" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K508" s="8"/>
       <c r="L508" s="8"/>
     </row>
@@ -22040,7 +23074,9 @@
         <v>1808</v>
       </c>
       <c r="I509" s="4"/>
-      <c r="J509" s="7"/>
+      <c r="J509" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K509" s="8"/>
       <c r="L509" s="8"/>
     </row>
@@ -22068,7 +23104,9 @@
         <v>1812</v>
       </c>
       <c r="I510" s="4"/>
-      <c r="J510" s="7"/>
+      <c r="J510" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K510" s="8"/>
       <c r="L510" s="8"/>
     </row>
@@ -22094,7 +23132,9 @@
       <c r="G511" s="3"/>
       <c r="H511" s="4"/>
       <c r="I511" s="4"/>
-      <c r="J511" s="7"/>
+      <c r="J511" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K511" s="8"/>
       <c r="L511" s="8"/>
     </row>
@@ -22122,7 +23162,9 @@
         <v>1819</v>
       </c>
       <c r="I512" s="4"/>
-      <c r="J512" s="7"/>
+      <c r="J512" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K512" s="8"/>
       <c r="L512" s="8"/>
     </row>
@@ -22148,7 +23190,9 @@
       <c r="G513" s="3"/>
       <c r="H513" s="4"/>
       <c r="I513" s="4"/>
-      <c r="J513" s="7"/>
+      <c r="J513" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K513" s="8"/>
       <c r="L513" s="8"/>
     </row>
@@ -22174,7 +23218,9 @@
       <c r="G514" s="3"/>
       <c r="H514" s="4"/>
       <c r="I514" s="4"/>
-      <c r="J514" s="7"/>
+      <c r="J514" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K514" s="8"/>
       <c r="L514" s="8"/>
     </row>
@@ -22204,7 +23250,9 @@
         <v>1830</v>
       </c>
       <c r="I515" s="4"/>
-      <c r="J515" s="7"/>
+      <c r="J515" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K515" s="8"/>
       <c r="L515" s="8"/>
     </row>
@@ -22234,7 +23282,9 @@
         <v>1835</v>
       </c>
       <c r="I516" s="4"/>
-      <c r="J516" s="7"/>
+      <c r="J516" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K516" s="8"/>
       <c r="L516" s="8"/>
     </row>
@@ -22264,7 +23314,9 @@
         <v>1830</v>
       </c>
       <c r="I517" s="4"/>
-      <c r="J517" s="7"/>
+      <c r="J517" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K517" s="8"/>
       <c r="L517" s="8"/>
     </row>
@@ -22290,7 +23342,9 @@
       <c r="G518" s="3"/>
       <c r="H518" s="4"/>
       <c r="I518" s="4"/>
-      <c r="J518" s="7"/>
+      <c r="J518" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K518" s="8"/>
       <c r="L518" s="8"/>
     </row>
@@ -22314,7 +23368,9 @@
       <c r="G519" s="3"/>
       <c r="H519" s="4"/>
       <c r="I519" s="4"/>
-      <c r="J519" s="7"/>
+      <c r="J519" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K519" s="8"/>
       <c r="L519" s="8"/>
     </row>
@@ -22340,7 +23396,9 @@
       <c r="G520" s="3"/>
       <c r="H520" s="4"/>
       <c r="I520" s="4"/>
-      <c r="J520" s="7"/>
+      <c r="J520" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K520" s="8"/>
       <c r="L520" s="8"/>
     </row>
@@ -22370,7 +23428,9 @@
         <v>1853</v>
       </c>
       <c r="I521" s="4"/>
-      <c r="J521" s="7"/>
+      <c r="J521" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K521" s="8"/>
       <c r="L521" s="8"/>
     </row>
@@ -22396,7 +23456,9 @@
       <c r="G522" s="3"/>
       <c r="H522" s="4"/>
       <c r="I522" s="4"/>
-      <c r="J522" s="7"/>
+      <c r="J522" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K522" s="8"/>
       <c r="L522" s="8"/>
     </row>
@@ -22420,7 +23482,9 @@
       <c r="G523" s="3"/>
       <c r="H523" s="4"/>
       <c r="I523" s="4"/>
-      <c r="J523" s="7"/>
+      <c r="J523" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K523" s="8"/>
       <c r="L523" s="8"/>
     </row>
@@ -22450,7 +23514,9 @@
         <v>1864</v>
       </c>
       <c r="I524" s="4"/>
-      <c r="J524" s="7"/>
+      <c r="J524" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K524" s="8"/>
       <c r="L524" s="8"/>
     </row>
@@ -22476,7 +23542,9 @@
       <c r="G525" s="3"/>
       <c r="H525" s="4"/>
       <c r="I525" s="4"/>
-      <c r="J525" s="7"/>
+      <c r="J525" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K525" s="8"/>
       <c r="L525" s="8"/>
     </row>
@@ -22500,7 +23568,9 @@
       <c r="G526" s="3"/>
       <c r="H526" s="4"/>
       <c r="I526" s="4"/>
-      <c r="J526" s="7"/>
+      <c r="J526" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K526" s="8"/>
       <c r="L526" s="8"/>
     </row>
@@ -22526,7 +23596,9 @@
       <c r="G527" s="3"/>
       <c r="H527" s="4"/>
       <c r="I527" s="4"/>
-      <c r="J527" s="7"/>
+      <c r="J527" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K527" s="8"/>
       <c r="L527" s="8"/>
     </row>
@@ -22550,7 +23622,9 @@
       <c r="G528" s="3"/>
       <c r="H528" s="4"/>
       <c r="I528" s="4"/>
-      <c r="J528" s="7"/>
+      <c r="J528" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K528" s="8"/>
       <c r="L528" s="8"/>
     </row>
@@ -22574,7 +23648,9 @@
       <c r="G529" s="3"/>
       <c r="H529" s="4"/>
       <c r="I529" s="4"/>
-      <c r="J529" s="7"/>
+      <c r="J529" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K529" s="8"/>
       <c r="L529" s="8"/>
     </row>
@@ -22598,7 +23674,9 @@
       <c r="G530" s="3"/>
       <c r="H530" s="4"/>
       <c r="I530" s="4"/>
-      <c r="J530" s="7"/>
+      <c r="J530" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K530" s="8"/>
       <c r="L530" s="8"/>
     </row>
@@ -22622,7 +23700,9 @@
       <c r="G531" s="3"/>
       <c r="H531" s="4"/>
       <c r="I531" s="4"/>
-      <c r="J531" s="7"/>
+      <c r="J531" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K531" s="8"/>
       <c r="L531" s="8"/>
     </row>
@@ -22646,7 +23726,9 @@
       <c r="G532" s="3"/>
       <c r="H532" s="4"/>
       <c r="I532" s="4"/>
-      <c r="J532" s="7"/>
+      <c r="J532" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K532" s="8"/>
       <c r="L532" s="8"/>
     </row>
@@ -22670,7 +23752,9 @@
       <c r="G533" s="3"/>
       <c r="H533" s="4"/>
       <c r="I533" s="4"/>
-      <c r="J533" s="7"/>
+      <c r="J533" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K533" s="8"/>
       <c r="L533" s="8"/>
     </row>
@@ -22700,7 +23784,9 @@
         <v>1894</v>
       </c>
       <c r="I534" s="4"/>
-      <c r="J534" s="7"/>
+      <c r="J534" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K534" s="8"/>
       <c r="L534" s="8"/>
     </row>
@@ -22726,7 +23812,9 @@
       <c r="G535" s="3"/>
       <c r="H535" s="4"/>
       <c r="I535" s="4"/>
-      <c r="J535" s="7"/>
+      <c r="J535" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K535" s="8"/>
       <c r="L535" s="8"/>
     </row>
@@ -22750,7 +23838,9 @@
       <c r="G536" s="3"/>
       <c r="H536" s="4"/>
       <c r="I536" s="4"/>
-      <c r="J536" s="7"/>
+      <c r="J536" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K536" s="8"/>
       <c r="L536" s="8"/>
     </row>
@@ -22774,7 +23864,9 @@
       <c r="G537" s="3"/>
       <c r="H537" s="4"/>
       <c r="I537" s="4"/>
-      <c r="J537" s="7"/>
+      <c r="J537" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K537" s="8"/>
       <c r="L537" s="8"/>
     </row>
@@ -22798,7 +23890,9 @@
       <c r="G538" s="3"/>
       <c r="H538" s="4"/>
       <c r="I538" s="4"/>
-      <c r="J538" s="7"/>
+      <c r="J538" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K538" s="8"/>
       <c r="L538" s="8"/>
     </row>
@@ -22826,7 +23920,9 @@
         <v>1909</v>
       </c>
       <c r="I539" s="4"/>
-      <c r="J539" s="7"/>
+      <c r="J539" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K539" s="8"/>
       <c r="L539" s="8"/>
     </row>
@@ -22850,7 +23946,9 @@
       <c r="G540" s="3"/>
       <c r="H540" s="4"/>
       <c r="I540" s="4"/>
-      <c r="J540" s="7"/>
+      <c r="J540" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K540" s="8"/>
       <c r="L540" s="8"/>
     </row>
@@ -22874,7 +23972,9 @@
       <c r="G541" s="3"/>
       <c r="H541" s="4"/>
       <c r="I541" s="4"/>
-      <c r="J541" s="7"/>
+      <c r="J541" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K541" s="8"/>
       <c r="L541" s="8"/>
     </row>
@@ -22902,7 +24002,9 @@
         <v>1919</v>
       </c>
       <c r="I542" s="4"/>
-      <c r="J542" s="7"/>
+      <c r="J542" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K542" s="8"/>
       <c r="L542" s="8"/>
     </row>
@@ -22930,7 +24032,9 @@
         <v>1919</v>
       </c>
       <c r="I543" s="4"/>
-      <c r="J543" s="7"/>
+      <c r="J543" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K543" s="8"/>
       <c r="L543" s="8"/>
     </row>
@@ -22958,7 +24062,9 @@
         <v>1919</v>
       </c>
       <c r="I544" s="4"/>
-      <c r="J544" s="7"/>
+      <c r="J544" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K544" s="8"/>
       <c r="L544" s="8"/>
     </row>
@@ -22988,7 +24094,9 @@
         <v>1930</v>
       </c>
       <c r="I545" s="4"/>
-      <c r="J545" s="7"/>
+      <c r="J545" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K545" s="8"/>
       <c r="L545" s="8"/>
     </row>
@@ -23014,7 +24122,9 @@
       <c r="G546" s="3"/>
       <c r="H546" s="4"/>
       <c r="I546" s="4"/>
-      <c r="J546" s="7"/>
+      <c r="J546" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K546" s="8"/>
       <c r="L546" s="8"/>
     </row>
@@ -23040,7 +24150,9 @@
       <c r="G547" s="3"/>
       <c r="H547" s="4"/>
       <c r="I547" s="4"/>
-      <c r="J547" s="7"/>
+      <c r="J547" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K547" s="8"/>
       <c r="L547" s="8"/>
     </row>
@@ -23066,7 +24178,9 @@
       <c r="G548" s="3"/>
       <c r="H548" s="4"/>
       <c r="I548" s="4"/>
-      <c r="J548" s="7"/>
+      <c r="J548" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K548" s="8"/>
       <c r="L548" s="8"/>
     </row>
@@ -23092,7 +24206,9 @@
       <c r="G549" s="3"/>
       <c r="H549" s="4"/>
       <c r="I549" s="4"/>
-      <c r="J549" s="7"/>
+      <c r="J549" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K549" s="8"/>
       <c r="L549" s="8"/>
     </row>
@@ -23122,7 +24238,9 @@
         <v>1427</v>
       </c>
       <c r="I550" s="4"/>
-      <c r="J550" s="7"/>
+      <c r="J550" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K550" s="8"/>
       <c r="L550" s="8"/>
     </row>
@@ -23148,7 +24266,9 @@
       <c r="G551" s="3"/>
       <c r="H551" s="4"/>
       <c r="I551" s="4"/>
-      <c r="J551" s="7"/>
+      <c r="J551" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K551" s="8"/>
       <c r="L551" s="8"/>
     </row>
@@ -23172,7 +24292,9 @@
       <c r="G552" s="3"/>
       <c r="H552" s="4"/>
       <c r="I552" s="4"/>
-      <c r="J552" s="7"/>
+      <c r="J552" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K552" s="8"/>
       <c r="L552" s="8"/>
     </row>
@@ -23198,7 +24320,9 @@
       <c r="G553" s="3"/>
       <c r="H553" s="4"/>
       <c r="I553" s="4"/>
-      <c r="J553" s="7"/>
+      <c r="J553" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K553" s="8"/>
       <c r="L553" s="8"/>
     </row>
@@ -23226,7 +24350,9 @@
         <v>1959</v>
       </c>
       <c r="I554" s="4"/>
-      <c r="J554" s="7"/>
+      <c r="J554" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K554" s="8"/>
       <c r="L554" s="8"/>
     </row>
@@ -23252,7 +24378,9 @@
       <c r="G555" s="3"/>
       <c r="H555" s="4"/>
       <c r="I555" s="4"/>
-      <c r="J555" s="7"/>
+      <c r="J555" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K555" s="8"/>
       <c r="L555" s="8"/>
     </row>
@@ -23278,7 +24406,9 @@
       <c r="G556" s="3"/>
       <c r="H556" s="4"/>
       <c r="I556" s="4"/>
-      <c r="J556" s="7"/>
+      <c r="J556" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K556" s="8"/>
       <c r="L556" s="8"/>
     </row>
@@ -23308,7 +24438,9 @@
         <v>1970</v>
       </c>
       <c r="I557" s="4"/>
-      <c r="J557" s="7"/>
+      <c r="J557" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K557" s="8"/>
       <c r="L557" s="8"/>
     </row>
@@ -23332,7 +24464,9 @@
       <c r="G558" s="3"/>
       <c r="H558" s="4"/>
       <c r="I558" s="4"/>
-      <c r="J558" s="7"/>
+      <c r="J558" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K558" s="8"/>
       <c r="L558" s="8"/>
     </row>
@@ -23358,7 +24492,9 @@
       <c r="G559" s="3"/>
       <c r="H559" s="4"/>
       <c r="I559" s="4"/>
-      <c r="J559" s="7"/>
+      <c r="J559" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K559" s="8"/>
       <c r="L559" s="8"/>
     </row>
@@ -23382,7 +24518,9 @@
       <c r="G560" s="3"/>
       <c r="H560" s="4"/>
       <c r="I560" s="4"/>
-      <c r="J560" s="7"/>
+      <c r="J560" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K560" s="8"/>
       <c r="L560" s="8"/>
     </row>
@@ -23408,7 +24546,9 @@
       <c r="I561" s="10" t="s">
         <v>1981</v>
       </c>
-      <c r="J561" s="7"/>
+      <c r="J561" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K561" s="8"/>
       <c r="L561" s="8"/>
     </row>
@@ -23432,7 +24572,9 @@
       <c r="G562" s="3"/>
       <c r="H562" s="4"/>
       <c r="I562" s="4"/>
-      <c r="J562" s="7"/>
+      <c r="J562" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K562" s="8"/>
       <c r="L562" s="8"/>
     </row>
@@ -23458,7 +24600,9 @@
       <c r="G563" s="3"/>
       <c r="H563" s="4"/>
       <c r="I563" s="4"/>
-      <c r="J563" s="7"/>
+      <c r="J563" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K563" s="8"/>
       <c r="L563" s="8"/>
     </row>
@@ -23486,7 +24630,9 @@
         <v>1991</v>
       </c>
       <c r="I564" s="4"/>
-      <c r="J564" s="7"/>
+      <c r="J564" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K564" s="8"/>
       <c r="L564" s="8"/>
     </row>
@@ -23510,7 +24656,9 @@
       <c r="G565" s="3"/>
       <c r="H565" s="4"/>
       <c r="I565" s="4"/>
-      <c r="J565" s="7"/>
+      <c r="J565" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K565" s="8"/>
       <c r="L565" s="8"/>
     </row>
@@ -23534,7 +24682,9 @@
       <c r="G566" s="3"/>
       <c r="H566" s="4"/>
       <c r="I566" s="4"/>
-      <c r="J566" s="7"/>
+      <c r="J566" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K566" s="8"/>
       <c r="L566" s="8"/>
     </row>
@@ -23558,7 +24708,9 @@
       <c r="G567" s="3"/>
       <c r="H567" s="4"/>
       <c r="I567" s="4"/>
-      <c r="J567" s="7"/>
+      <c r="J567" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K567" s="8"/>
       <c r="L567" s="8"/>
     </row>
@@ -23588,7 +24740,9 @@
         <v>2002</v>
       </c>
       <c r="I568" s="4"/>
-      <c r="J568" s="7"/>
+      <c r="J568" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K568" s="8"/>
       <c r="L568" s="8"/>
     </row>
@@ -23618,7 +24772,9 @@
         <v>2002</v>
       </c>
       <c r="I569" s="4"/>
-      <c r="J569" s="7"/>
+      <c r="J569" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K569" s="8"/>
       <c r="L569" s="8"/>
     </row>
@@ -23644,7 +24800,9 @@
       <c r="I570" s="10" t="s">
         <v>1556</v>
       </c>
-      <c r="J570" s="7"/>
+      <c r="J570" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K570" s="8"/>
       <c r="L570" s="8"/>
     </row>
@@ -23668,7 +24826,9 @@
       <c r="G571" s="3"/>
       <c r="H571" s="4"/>
       <c r="I571" s="4"/>
-      <c r="J571" s="7"/>
+      <c r="J571" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K571" s="8"/>
       <c r="L571" s="8"/>
     </row>
@@ -23692,7 +24852,9 @@
       <c r="G572" s="3"/>
       <c r="H572" s="4"/>
       <c r="I572" s="4"/>
-      <c r="J572" s="7"/>
+      <c r="J572" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K572" s="8"/>
       <c r="L572" s="8"/>
     </row>
@@ -23718,7 +24880,9 @@
       <c r="G573" s="3"/>
       <c r="H573" s="4"/>
       <c r="I573" s="4"/>
-      <c r="J573" s="7"/>
+      <c r="J573" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K573" s="8"/>
       <c r="L573" s="8"/>
     </row>
@@ -23744,7 +24908,9 @@
       <c r="I574" s="10" t="s">
         <v>2021</v>
       </c>
-      <c r="J574" s="7"/>
+      <c r="J574" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K574" s="8"/>
       <c r="L574" s="8"/>
     </row>
@@ -23774,7 +24940,9 @@
         <v>2026</v>
       </c>
       <c r="I575" s="4"/>
-      <c r="J575" s="7"/>
+      <c r="J575" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K575" s="8"/>
       <c r="L575" s="8"/>
     </row>
@@ -23800,7 +24968,9 @@
       <c r="G576" s="3"/>
       <c r="H576" s="4"/>
       <c r="I576" s="4"/>
-      <c r="J576" s="7"/>
+      <c r="J576" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K576" s="8"/>
       <c r="L576" s="8"/>
     </row>
@@ -23824,7 +24994,9 @@
       <c r="G577" s="3"/>
       <c r="H577" s="4"/>
       <c r="I577" s="4"/>
-      <c r="J577" s="7"/>
+      <c r="J577" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K577" s="8"/>
       <c r="L577" s="8"/>
     </row>
@@ -23850,7 +25022,9 @@
       <c r="G578" s="3"/>
       <c r="H578" s="4"/>
       <c r="I578" s="4"/>
-      <c r="J578" s="7"/>
+      <c r="J578" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K578" s="8"/>
       <c r="L578" s="8"/>
     </row>
@@ -23876,7 +25050,9 @@
       <c r="G579" s="3"/>
       <c r="H579" s="4"/>
       <c r="I579" s="4"/>
-      <c r="J579" s="7"/>
+      <c r="J579" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K579" s="8"/>
       <c r="L579" s="8"/>
     </row>
@@ -23902,7 +25078,9 @@
       <c r="G580" s="3"/>
       <c r="H580" s="4"/>
       <c r="I580" s="4"/>
-      <c r="J580" s="7"/>
+      <c r="J580" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K580" s="8"/>
       <c r="L580" s="8"/>
     </row>
@@ -23928,7 +25106,9 @@
       <c r="G581" s="3"/>
       <c r="H581" s="4"/>
       <c r="I581" s="4"/>
-      <c r="J581" s="7"/>
+      <c r="J581" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K581" s="8"/>
       <c r="L581" s="8"/>
     </row>
@@ -23952,7 +25132,9 @@
       <c r="G582" s="3"/>
       <c r="H582" s="4"/>
       <c r="I582" s="4"/>
-      <c r="J582" s="7"/>
+      <c r="J582" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K582" s="8"/>
       <c r="L582" s="8"/>
     </row>
@@ -23976,7 +25158,9 @@
       <c r="G583" s="3"/>
       <c r="H583" s="4"/>
       <c r="I583" s="4"/>
-      <c r="J583" s="7"/>
+      <c r="J583" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K583" s="8"/>
       <c r="L583" s="8"/>
     </row>
@@ -24000,7 +25184,9 @@
       <c r="G584" s="3"/>
       <c r="H584" s="4"/>
       <c r="I584" s="4"/>
-      <c r="J584" s="7"/>
+      <c r="J584" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K584" s="8"/>
       <c r="L584" s="8"/>
     </row>
@@ -24024,7 +25210,9 @@
       <c r="G585" s="3"/>
       <c r="H585" s="4"/>
       <c r="I585" s="4"/>
-      <c r="J585" s="7"/>
+      <c r="J585" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K585" s="8"/>
       <c r="L585" s="8"/>
     </row>
@@ -24052,7 +25240,9 @@
       <c r="I586" s="10" t="s">
         <v>1479</v>
       </c>
-      <c r="J586" s="7"/>
+      <c r="J586" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K586" s="8"/>
       <c r="L586" s="8"/>
     </row>
@@ -24076,7 +25266,9 @@
       <c r="G587" s="3"/>
       <c r="H587" s="4"/>
       <c r="I587" s="4"/>
-      <c r="J587" s="7"/>
+      <c r="J587" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K587" s="8"/>
       <c r="L587" s="8"/>
     </row>
@@ -24102,7 +25294,9 @@
       <c r="G588" s="3"/>
       <c r="H588" s="4"/>
       <c r="I588" s="4"/>
-      <c r="J588" s="7"/>
+      <c r="J588" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K588" s="8"/>
       <c r="L588" s="8"/>
     </row>
@@ -24128,7 +25322,9 @@
       <c r="G589" s="3"/>
       <c r="H589" s="4"/>
       <c r="I589" s="4"/>
-      <c r="J589" s="7"/>
+      <c r="J589" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K589" s="8"/>
       <c r="L589" s="8"/>
     </row>
@@ -24154,7 +25350,9 @@
       <c r="G590" s="3"/>
       <c r="H590" s="4"/>
       <c r="I590" s="4"/>
-      <c r="J590" s="7"/>
+      <c r="J590" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K590" s="8"/>
       <c r="L590" s="8"/>
     </row>
@@ -24180,7 +25378,9 @@
       <c r="G591" s="3"/>
       <c r="H591" s="4"/>
       <c r="I591" s="4"/>
-      <c r="J591" s="7"/>
+      <c r="J591" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K591" s="8"/>
       <c r="L591" s="8"/>
     </row>
@@ -24206,7 +25406,9 @@
       <c r="G592" s="3"/>
       <c r="H592" s="4"/>
       <c r="I592" s="4"/>
-      <c r="J592" s="7"/>
+      <c r="J592" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K592" s="8"/>
       <c r="L592" s="8"/>
     </row>
@@ -24232,7 +25434,9 @@
       <c r="G593" s="3"/>
       <c r="H593" s="4"/>
       <c r="I593" s="4"/>
-      <c r="J593" s="7"/>
+      <c r="J593" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K593" s="8"/>
       <c r="L593" s="8"/>
     </row>
@@ -24256,7 +25460,9 @@
       <c r="G594" s="3"/>
       <c r="H594" s="4"/>
       <c r="I594" s="4"/>
-      <c r="J594" s="7"/>
+      <c r="J594" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K594" s="8"/>
       <c r="L594" s="8"/>
     </row>
@@ -24280,7 +25486,9 @@
       <c r="G595" s="3"/>
       <c r="H595" s="4"/>
       <c r="I595" s="4"/>
-      <c r="J595" s="7"/>
+      <c r="J595" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K595" s="8"/>
       <c r="L595" s="8"/>
     </row>
@@ -24306,7 +25514,9 @@
       <c r="G596" s="3"/>
       <c r="H596" s="4"/>
       <c r="I596" s="4"/>
-      <c r="J596" s="7"/>
+      <c r="J596" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K596" s="8"/>
       <c r="L596" s="8"/>
     </row>
@@ -24332,7 +25542,9 @@
       <c r="G597" s="3"/>
       <c r="H597" s="4"/>
       <c r="I597" s="4"/>
-      <c r="J597" s="7"/>
+      <c r="J597" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K597" s="8"/>
       <c r="L597" s="8"/>
     </row>
@@ -24356,7 +25568,9 @@
       <c r="G598" s="3"/>
       <c r="H598" s="4"/>
       <c r="I598" s="4"/>
-      <c r="J598" s="7"/>
+      <c r="J598" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K598" s="8"/>
       <c r="L598" s="8"/>
     </row>
@@ -24384,7 +25598,9 @@
         <v>2087</v>
       </c>
       <c r="I599" s="4"/>
-      <c r="J599" s="7"/>
+      <c r="J599" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K599" s="8"/>
       <c r="L599" s="8"/>
     </row>
@@ -24412,7 +25628,9 @@
       <c r="I600" s="10" t="s">
         <v>1479</v>
       </c>
-      <c r="J600" s="7"/>
+      <c r="J600" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K600" s="8"/>
       <c r="L600" s="8"/>
     </row>
@@ -24440,7 +25658,9 @@
       <c r="I601" s="10" t="s">
         <v>1479</v>
       </c>
-      <c r="J601" s="7"/>
+      <c r="J601" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K601" s="8"/>
       <c r="L601" s="8"/>
     </row>
@@ -24470,7 +25690,9 @@
         <v>2098</v>
       </c>
       <c r="I602" s="4"/>
-      <c r="J602" s="7"/>
+      <c r="J602" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K602" s="8"/>
       <c r="L602" s="8"/>
     </row>
@@ -24500,7 +25722,9 @@
         <v>2103</v>
       </c>
       <c r="I603" s="4"/>
-      <c r="J603" s="7"/>
+      <c r="J603" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K603" s="8"/>
       <c r="L603" s="8"/>
     </row>
@@ -24530,7 +25754,9 @@
         <v>2108</v>
       </c>
       <c r="I604" s="4"/>
-      <c r="J604" s="7"/>
+      <c r="J604" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K604" s="8"/>
       <c r="L604" s="8"/>
     </row>
@@ -24556,7 +25782,9 @@
       <c r="G605" s="3"/>
       <c r="H605" s="4"/>
       <c r="I605" s="4"/>
-      <c r="J605" s="7"/>
+      <c r="J605" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K605" s="8"/>
       <c r="L605" s="8"/>
     </row>
@@ -24582,7 +25810,9 @@
       <c r="G606" s="3"/>
       <c r="H606" s="4"/>
       <c r="I606" s="4"/>
-      <c r="J606" s="7"/>
+      <c r="J606" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K606" s="8"/>
       <c r="L606" s="8"/>
     </row>
@@ -24608,7 +25838,9 @@
       <c r="G607" s="3"/>
       <c r="H607" s="4"/>
       <c r="I607" s="4"/>
-      <c r="J607" s="7"/>
+      <c r="J607" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K607" s="8"/>
       <c r="L607" s="8"/>
     </row>
@@ -24634,7 +25866,9 @@
       <c r="G608" s="3"/>
       <c r="H608" s="4"/>
       <c r="I608" s="4"/>
-      <c r="J608" s="7"/>
+      <c r="J608" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K608" s="8"/>
       <c r="L608" s="8"/>
     </row>
@@ -24660,7 +25894,9 @@
       <c r="G609" s="3"/>
       <c r="H609" s="4"/>
       <c r="I609" s="4"/>
-      <c r="J609" s="7"/>
+      <c r="J609" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K609" s="8"/>
       <c r="L609" s="8"/>
     </row>
@@ -24686,7 +25922,9 @@
       <c r="G610" s="3"/>
       <c r="H610" s="4"/>
       <c r="I610" s="4"/>
-      <c r="J610" s="7"/>
+      <c r="J610" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K610" s="8"/>
       <c r="L610" s="8"/>
     </row>
@@ -24710,7 +25948,9 @@
       <c r="G611" s="3"/>
       <c r="H611" s="4"/>
       <c r="I611" s="4"/>
-      <c r="J611" s="7"/>
+      <c r="J611" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K611" s="8"/>
       <c r="L611" s="8"/>
     </row>
@@ -24734,7 +25974,9 @@
       <c r="G612" s="3"/>
       <c r="H612" s="4"/>
       <c r="I612" s="4"/>
-      <c r="J612" s="7"/>
+      <c r="J612" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K612" s="8"/>
       <c r="L612" s="8"/>
     </row>
@@ -24758,7 +26000,9 @@
       <c r="G613" s="3"/>
       <c r="H613" s="4"/>
       <c r="I613" s="4"/>
-      <c r="J613" s="7"/>
+      <c r="J613" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K613" s="8"/>
       <c r="L613" s="8"/>
     </row>
@@ -24788,7 +26032,9 @@
       <c r="I614" s="10" t="s">
         <v>2136</v>
       </c>
-      <c r="J614" s="7"/>
+      <c r="J614" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K614" s="8"/>
       <c r="L614" s="8"/>
     </row>
@@ -24814,7 +26060,9 @@
       <c r="I615" s="10" t="s">
         <v>2140</v>
       </c>
-      <c r="J615" s="7"/>
+      <c r="J615" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K615" s="8"/>
       <c r="L615" s="8"/>
     </row>
@@ -24838,7 +26086,9 @@
       <c r="G616" s="3"/>
       <c r="H616" s="4"/>
       <c r="I616" s="4"/>
-      <c r="J616" s="7"/>
+      <c r="J616" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K616" s="8"/>
       <c r="L616" s="8"/>
     </row>
@@ -24866,7 +26116,9 @@
         <v>2147</v>
       </c>
       <c r="I617" s="4"/>
-      <c r="J617" s="7"/>
+      <c r="J617" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K617" s="8"/>
       <c r="L617" s="8"/>
     </row>
@@ -24890,7 +26142,9 @@
       <c r="G618" s="3"/>
       <c r="H618" s="4"/>
       <c r="I618" s="4"/>
-      <c r="J618" s="7"/>
+      <c r="J618" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K618" s="8"/>
       <c r="L618" s="8"/>
     </row>
@@ -24914,7 +26168,9 @@
       <c r="G619" s="3"/>
       <c r="H619" s="4"/>
       <c r="I619" s="4"/>
-      <c r="J619" s="7"/>
+      <c r="J619" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K619" s="8"/>
       <c r="L619" s="8"/>
     </row>
@@ -24938,7 +26194,9 @@
       <c r="G620" s="3"/>
       <c r="H620" s="4"/>
       <c r="I620" s="4"/>
-      <c r="J620" s="7"/>
+      <c r="J620" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K620" s="8"/>
       <c r="L620" s="8"/>
     </row>
@@ -24962,7 +26220,9 @@
       <c r="G621" s="3"/>
       <c r="H621" s="4"/>
       <c r="I621" s="4"/>
-      <c r="J621" s="7"/>
+      <c r="J621" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K621" s="8"/>
       <c r="L621" s="8"/>
     </row>
@@ -24988,7 +26248,9 @@
       <c r="G622" s="3"/>
       <c r="H622" s="4"/>
       <c r="I622" s="4"/>
-      <c r="J622" s="7"/>
+      <c r="J622" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K622" s="8"/>
       <c r="L622" s="8"/>
     </row>
@@ -25014,7 +26276,9 @@
       <c r="G623" s="3"/>
       <c r="H623" s="4"/>
       <c r="I623" s="4"/>
-      <c r="J623" s="7"/>
+      <c r="J623" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K623" s="8"/>
       <c r="L623" s="8"/>
     </row>
@@ -25044,7 +26308,9 @@
         <v>2168</v>
       </c>
       <c r="I624" s="4"/>
-      <c r="J624" s="7"/>
+      <c r="J624" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K624" s="8"/>
       <c r="L624" s="8"/>
     </row>
@@ -25070,7 +26336,9 @@
       <c r="G625" s="3"/>
       <c r="H625" s="4"/>
       <c r="I625" s="4"/>
-      <c r="J625" s="7"/>
+      <c r="J625" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K625" s="8"/>
       <c r="L625" s="8"/>
     </row>
@@ -25096,7 +26364,9 @@
       <c r="G626" s="3"/>
       <c r="H626" s="4"/>
       <c r="I626" s="4"/>
-      <c r="J626" s="7"/>
+      <c r="J626" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K626" s="8"/>
       <c r="L626" s="8"/>
     </row>
@@ -25122,7 +26392,9 @@
       <c r="G627" s="3"/>
       <c r="H627" s="4"/>
       <c r="I627" s="4"/>
-      <c r="J627" s="7"/>
+      <c r="J627" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K627" s="8"/>
       <c r="L627" s="8"/>
     </row>
@@ -25152,7 +26424,9 @@
         <v>2181</v>
       </c>
       <c r="I628" s="4"/>
-      <c r="J628" s="7"/>
+      <c r="J628" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K628" s="8"/>
       <c r="L628" s="8"/>
     </row>
@@ -25176,7 +26450,9 @@
       <c r="G629" s="3"/>
       <c r="H629" s="4"/>
       <c r="I629" s="4"/>
-      <c r="J629" s="7"/>
+      <c r="J629" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K629" s="8"/>
       <c r="L629" s="8"/>
     </row>
@@ -25200,7 +26476,9 @@
       <c r="G630" s="3"/>
       <c r="H630" s="4"/>
       <c r="I630" s="4"/>
-      <c r="J630" s="7"/>
+      <c r="J630" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K630" s="8"/>
       <c r="L630" s="8"/>
     </row>
@@ -25230,7 +26508,9 @@
         <v>2192</v>
       </c>
       <c r="I631" s="4"/>
-      <c r="J631" s="7"/>
+      <c r="J631" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K631" s="8"/>
       <c r="L631" s="8"/>
     </row>
@@ -25260,7 +26540,9 @@
         <v>1894</v>
       </c>
       <c r="I632" s="4"/>
-      <c r="J632" s="7"/>
+      <c r="J632" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K632" s="8"/>
       <c r="L632" s="8"/>
     </row>
@@ -25290,7 +26572,9 @@
         <v>1894</v>
       </c>
       <c r="I633" s="4"/>
-      <c r="J633" s="7"/>
+      <c r="J633" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K633" s="8"/>
       <c r="L633" s="8"/>
     </row>
@@ -25316,7 +26600,9 @@
       <c r="G634" s="3"/>
       <c r="H634" s="4"/>
       <c r="I634" s="4"/>
-      <c r="J634" s="7"/>
+      <c r="J634" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K634" s="8"/>
       <c r="L634" s="8"/>
     </row>
@@ -25340,7 +26626,9 @@
       <c r="G635" s="3"/>
       <c r="H635" s="4"/>
       <c r="I635" s="4"/>
-      <c r="J635" s="7"/>
+      <c r="J635" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K635" s="8"/>
       <c r="L635" s="8"/>
     </row>
@@ -25366,7 +26654,9 @@
       <c r="G636" s="3"/>
       <c r="H636" s="4"/>
       <c r="I636" s="4"/>
-      <c r="J636" s="7"/>
+      <c r="J636" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K636" s="8"/>
       <c r="L636" s="8"/>
     </row>
@@ -25390,7 +26680,9 @@
       <c r="G637" s="3"/>
       <c r="H637" s="4"/>
       <c r="I637" s="4"/>
-      <c r="J637" s="7"/>
+      <c r="J637" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K637" s="8"/>
       <c r="L637" s="8"/>
     </row>
@@ -25414,7 +26706,9 @@
       <c r="G638" s="3"/>
       <c r="H638" s="4"/>
       <c r="I638" s="4"/>
-      <c r="J638" s="7"/>
+      <c r="J638" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K638" s="8"/>
       <c r="L638" s="8"/>
     </row>
@@ -25442,7 +26736,9 @@
         <v>2217</v>
       </c>
       <c r="I639" s="4"/>
-      <c r="J639" s="7"/>
+      <c r="J639" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K639" s="8"/>
       <c r="L639" s="8"/>
     </row>
@@ -25466,7 +26762,9 @@
       <c r="G640" s="3"/>
       <c r="H640" s="4"/>
       <c r="I640" s="4"/>
-      <c r="J640" s="7"/>
+      <c r="J640" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K640" s="8"/>
       <c r="L640" s="8"/>
     </row>
@@ -25492,7 +26790,9 @@
       <c r="G641" s="3"/>
       <c r="H641" s="4"/>
       <c r="I641" s="4"/>
-      <c r="J641" s="7"/>
+      <c r="J641" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K641" s="8"/>
       <c r="L641" s="8"/>
     </row>
@@ -25516,7 +26816,9 @@
       <c r="G642" s="3"/>
       <c r="H642" s="4"/>
       <c r="I642" s="4"/>
-      <c r="J642" s="7"/>
+      <c r="J642" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K642" s="8"/>
       <c r="L642" s="8"/>
     </row>
@@ -25540,7 +26842,9 @@
       <c r="G643" s="3"/>
       <c r="H643" s="4"/>
       <c r="I643" s="4"/>
-      <c r="J643" s="7"/>
+      <c r="J643" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K643" s="8"/>
       <c r="L643" s="8"/>
     </row>
@@ -25570,7 +26874,9 @@
         <v>2233</v>
       </c>
       <c r="I644" s="4"/>
-      <c r="J644" s="7"/>
+      <c r="J644" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K644" s="8"/>
       <c r="L644" s="8"/>
     </row>
@@ -25594,7 +26900,9 @@
       <c r="G645" s="3"/>
       <c r="H645" s="4"/>
       <c r="I645" s="4"/>
-      <c r="J645" s="7"/>
+      <c r="J645" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K645" s="8"/>
       <c r="L645" s="8"/>
     </row>
@@ -25618,7 +26926,9 @@
       <c r="G646" s="3"/>
       <c r="H646" s="4"/>
       <c r="I646" s="4"/>
-      <c r="J646" s="7"/>
+      <c r="J646" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K646" s="8"/>
       <c r="L646" s="8"/>
     </row>
@@ -25642,7 +26952,9 @@
       <c r="G647" s="3"/>
       <c r="H647" s="4"/>
       <c r="I647" s="4"/>
-      <c r="J647" s="7"/>
+      <c r="J647" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K647" s="8"/>
       <c r="L647" s="8"/>
     </row>
@@ -25666,7 +26978,9 @@
       <c r="G648" s="3"/>
       <c r="H648" s="4"/>
       <c r="I648" s="4"/>
-      <c r="J648" s="7"/>
+      <c r="J648" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K648" s="8"/>
       <c r="L648" s="8"/>
     </row>
@@ -25690,7 +27004,9 @@
       <c r="G649" s="3"/>
       <c r="H649" s="4"/>
       <c r="I649" s="4"/>
-      <c r="J649" s="7"/>
+      <c r="J649" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K649" s="8"/>
       <c r="L649" s="8"/>
     </row>
@@ -25714,7 +27030,9 @@
       <c r="G650" s="3"/>
       <c r="H650" s="4"/>
       <c r="I650" s="4"/>
-      <c r="J650" s="7"/>
+      <c r="J650" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K650" s="8"/>
       <c r="L650" s="8"/>
     </row>
@@ -25740,7 +27058,9 @@
       <c r="G651" s="3"/>
       <c r="H651" s="4"/>
       <c r="I651" s="4"/>
-      <c r="J651" s="7"/>
+      <c r="J651" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K651" s="8"/>
       <c r="L651" s="8"/>
     </row>
@@ -25766,7 +27086,9 @@
       <c r="G652" s="3"/>
       <c r="H652" s="4"/>
       <c r="I652" s="4"/>
-      <c r="J652" s="7"/>
+      <c r="J652" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K652" s="8"/>
       <c r="L652" s="8"/>
     </row>
@@ -25796,7 +27118,9 @@
         <v>2262</v>
       </c>
       <c r="I653" s="4"/>
-      <c r="J653" s="7"/>
+      <c r="J653" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K653" s="8"/>
       <c r="L653" s="8"/>
     </row>
@@ -25822,7 +27146,9 @@
       <c r="G654" s="3"/>
       <c r="H654" s="4"/>
       <c r="I654" s="4"/>
-      <c r="J654" s="7"/>
+      <c r="J654" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K654" s="8"/>
       <c r="L654" s="8"/>
     </row>
@@ -25848,7 +27174,9 @@
       <c r="G655" s="3"/>
       <c r="H655" s="4"/>
       <c r="I655" s="4"/>
-      <c r="J655" s="7"/>
+      <c r="J655" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K655" s="8"/>
       <c r="L655" s="8"/>
     </row>
@@ -25874,7 +27202,9 @@
       <c r="G656" s="3"/>
       <c r="H656" s="4"/>
       <c r="I656" s="4"/>
-      <c r="J656" s="7"/>
+      <c r="J656" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K656" s="8"/>
       <c r="L656" s="8"/>
     </row>
@@ -25900,7 +27230,9 @@
       <c r="G657" s="3"/>
       <c r="H657" s="4"/>
       <c r="I657" s="4"/>
-      <c r="J657" s="7"/>
+      <c r="J657" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K657" s="8"/>
       <c r="L657" s="8"/>
     </row>
@@ -25926,7 +27258,9 @@
       <c r="G658" s="3"/>
       <c r="H658" s="4"/>
       <c r="I658" s="4"/>
-      <c r="J658" s="7"/>
+      <c r="J658" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K658" s="8"/>
       <c r="L658" s="8"/>
     </row>
@@ -25952,7 +27286,9 @@
       <c r="G659" s="3"/>
       <c r="H659" s="4"/>
       <c r="I659" s="4"/>
-      <c r="J659" s="7"/>
+      <c r="J659" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K659" s="8"/>
       <c r="L659" s="8"/>
     </row>
@@ -25976,7 +27312,9 @@
       <c r="G660" s="3"/>
       <c r="H660" s="4"/>
       <c r="I660" s="4"/>
-      <c r="J660" s="7"/>
+      <c r="J660" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K660" s="8"/>
       <c r="L660" s="8"/>
     </row>
@@ -26002,7 +27340,9 @@
       <c r="G661" s="3"/>
       <c r="H661" s="4"/>
       <c r="I661" s="4"/>
-      <c r="J661" s="7"/>
+      <c r="J661" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K661" s="8"/>
       <c r="L661" s="8"/>
     </row>
@@ -26028,7 +27368,9 @@
       <c r="G662" s="3"/>
       <c r="H662" s="4"/>
       <c r="I662" s="4"/>
-      <c r="J662" s="7"/>
+      <c r="J662" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K662" s="8"/>
       <c r="L662" s="8"/>
     </row>
@@ -26054,7 +27396,9 @@
       <c r="G663" s="3"/>
       <c r="H663" s="4"/>
       <c r="I663" s="4"/>
-      <c r="J663" s="7"/>
+      <c r="J663" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K663" s="8"/>
       <c r="L663" s="8"/>
     </row>
@@ -26078,7 +27422,9 @@
       <c r="G664" s="3"/>
       <c r="H664" s="4"/>
       <c r="I664" s="4"/>
-      <c r="J664" s="7"/>
+      <c r="J664" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K664" s="8"/>
       <c r="L664" s="8"/>
     </row>
@@ -26102,7 +27448,9 @@
       <c r="G665" s="3"/>
       <c r="H665" s="4"/>
       <c r="I665" s="4"/>
-      <c r="J665" s="7"/>
+      <c r="J665" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K665" s="8"/>
       <c r="L665" s="8"/>
     </row>
@@ -26128,7 +27476,9 @@
       <c r="G666" s="3"/>
       <c r="H666" s="4"/>
       <c r="I666" s="4"/>
-      <c r="J666" s="7"/>
+      <c r="J666" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K666" s="8"/>
       <c r="L666" s="8"/>
     </row>
@@ -26152,7 +27502,9 @@
       <c r="G667" s="3"/>
       <c r="H667" s="4"/>
       <c r="I667" s="4"/>
-      <c r="J667" s="7"/>
+      <c r="J667" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K667" s="8"/>
       <c r="L667" s="8"/>
     </row>
@@ -26176,7 +27528,9 @@
       <c r="G668" s="3"/>
       <c r="H668" s="4"/>
       <c r="I668" s="4"/>
-      <c r="J668" s="7"/>
+      <c r="J668" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K668" s="8"/>
       <c r="L668" s="8"/>
     </row>
@@ -26202,7 +27556,9 @@
       <c r="G669" s="3"/>
       <c r="H669" s="4"/>
       <c r="I669" s="4"/>
-      <c r="J669" s="7"/>
+      <c r="J669" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K669" s="8"/>
       <c r="L669" s="8"/>
     </row>
@@ -26228,7 +27584,9 @@
       <c r="G670" s="3"/>
       <c r="H670" s="4"/>
       <c r="I670" s="4"/>
-      <c r="J670" s="7"/>
+      <c r="J670" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K670" s="8"/>
       <c r="L670" s="8"/>
     </row>
@@ -26254,7 +27612,9 @@
       <c r="G671" s="3"/>
       <c r="H671" s="4"/>
       <c r="I671" s="4"/>
-      <c r="J671" s="7"/>
+      <c r="J671" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K671" s="8"/>
       <c r="L671" s="8"/>
     </row>
@@ -26278,7 +27638,9 @@
       <c r="G672" s="3"/>
       <c r="H672" s="4"/>
       <c r="I672" s="4"/>
-      <c r="J672" s="7"/>
+      <c r="J672" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K672" s="8"/>
       <c r="L672" s="8"/>
     </row>
@@ -26302,7 +27664,9 @@
       <c r="G673" s="3"/>
       <c r="H673" s="4"/>
       <c r="I673" s="4"/>
-      <c r="J673" s="7"/>
+      <c r="J673" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K673" s="8"/>
       <c r="L673" s="8"/>
     </row>
@@ -26326,7 +27690,9 @@
       <c r="G674" s="3"/>
       <c r="H674" s="4"/>
       <c r="I674" s="4"/>
-      <c r="J674" s="7"/>
+      <c r="J674" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K674" s="8"/>
       <c r="L674" s="8"/>
     </row>
@@ -26352,7 +27718,9 @@
       <c r="G675" s="3"/>
       <c r="H675" s="4"/>
       <c r="I675" s="4"/>
-      <c r="J675" s="7"/>
+      <c r="J675" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K675" s="8"/>
       <c r="L675" s="8"/>
     </row>
@@ -26376,7 +27744,9 @@
       <c r="G676" s="3"/>
       <c r="H676" s="4"/>
       <c r="I676" s="4"/>
-      <c r="J676" s="7"/>
+      <c r="J676" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K676" s="8"/>
       <c r="L676" s="8"/>
     </row>
@@ -26402,7 +27772,9 @@
       <c r="G677" s="3"/>
       <c r="H677" s="4"/>
       <c r="I677" s="4"/>
-      <c r="J677" s="7"/>
+      <c r="J677" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K677" s="8"/>
       <c r="L677" s="8"/>
     </row>
@@ -26428,7 +27800,9 @@
       <c r="G678" s="3"/>
       <c r="H678" s="4"/>
       <c r="I678" s="4"/>
-      <c r="J678" s="7"/>
+      <c r="J678" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K678" s="8"/>
       <c r="L678" s="8"/>
     </row>
@@ -26458,7 +27832,9 @@
         <v>2327</v>
       </c>
       <c r="I679" s="4"/>
-      <c r="J679" s="7"/>
+      <c r="J679" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K679" s="8"/>
       <c r="L679" s="8"/>
     </row>
@@ -26484,7 +27860,9 @@
       <c r="G680" s="3"/>
       <c r="H680" s="4"/>
       <c r="I680" s="4"/>
-      <c r="J680" s="7"/>
+      <c r="J680" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K680" s="8"/>
       <c r="L680" s="8"/>
     </row>
@@ -26510,7 +27888,9 @@
       <c r="G681" s="3"/>
       <c r="H681" s="4"/>
       <c r="I681" s="4"/>
-      <c r="J681" s="7"/>
+      <c r="J681" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K681" s="8"/>
       <c r="L681" s="8"/>
     </row>
@@ -26536,7 +27916,9 @@
       <c r="G682" s="3"/>
       <c r="H682" s="4"/>
       <c r="I682" s="4"/>
-      <c r="J682" s="7"/>
+      <c r="J682" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K682" s="8"/>
       <c r="L682" s="8"/>
     </row>
@@ -26566,7 +27948,9 @@
         <v>1520</v>
       </c>
       <c r="I683" s="4"/>
-      <c r="J683" s="7"/>
+      <c r="J683" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K683" s="8"/>
       <c r="L683" s="8"/>
     </row>
@@ -26592,7 +27976,9 @@
       <c r="G684" s="3"/>
       <c r="H684" s="4"/>
       <c r="I684" s="4"/>
-      <c r="J684" s="7"/>
+      <c r="J684" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K684" s="8"/>
       <c r="L684" s="8"/>
     </row>
@@ -26622,7 +28008,9 @@
         <v>2348</v>
       </c>
       <c r="I685" s="4"/>
-      <c r="J685" s="7"/>
+      <c r="J685" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K685" s="8"/>
       <c r="L685" s="8"/>
     </row>
@@ -26648,7 +28036,9 @@
       <c r="G686" s="3"/>
       <c r="H686" s="4"/>
       <c r="I686" s="4"/>
-      <c r="J686" s="7"/>
+      <c r="J686" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K686" s="8"/>
       <c r="L686" s="8"/>
     </row>
@@ -26674,7 +28064,9 @@
       <c r="G687" s="3"/>
       <c r="H687" s="4"/>
       <c r="I687" s="4"/>
-      <c r="J687" s="7"/>
+      <c r="J687" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K687" s="8"/>
       <c r="L687" s="8"/>
     </row>
@@ -26704,7 +28096,9 @@
         <v>2359</v>
       </c>
       <c r="I688" s="4"/>
-      <c r="J688" s="7"/>
+      <c r="J688" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K688" s="8"/>
       <c r="L688" s="8"/>
     </row>
@@ -26734,7 +28128,9 @@
         <v>2364</v>
       </c>
       <c r="I689" s="4"/>
-      <c r="J689" s="7"/>
+      <c r="J689" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K689" s="8"/>
       <c r="L689" s="8"/>
     </row>
@@ -26760,7 +28156,9 @@
       <c r="G690" s="3"/>
       <c r="H690" s="4"/>
       <c r="I690" s="4"/>
-      <c r="J690" s="7"/>
+      <c r="J690" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K690" s="8"/>
       <c r="L690" s="8"/>
     </row>
@@ -26786,7 +28184,9 @@
       <c r="G691" s="3"/>
       <c r="H691" s="4"/>
       <c r="I691" s="4"/>
-      <c r="J691" s="7"/>
+      <c r="J691" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K691" s="8"/>
       <c r="L691" s="8"/>
     </row>
@@ -26812,7 +28212,9 @@
       <c r="G692" s="3"/>
       <c r="H692" s="4"/>
       <c r="I692" s="4"/>
-      <c r="J692" s="7"/>
+      <c r="J692" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K692" s="8"/>
       <c r="L692" s="8"/>
     </row>
@@ -26836,7 +28238,9 @@
       <c r="G693" s="3"/>
       <c r="H693" s="4"/>
       <c r="I693" s="4"/>
-      <c r="J693" s="7"/>
+      <c r="J693" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K693" s="8"/>
       <c r="L693" s="8"/>
     </row>
@@ -26860,7 +28264,9 @@
       <c r="G694" s="3"/>
       <c r="H694" s="4"/>
       <c r="I694" s="4"/>
-      <c r="J694" s="7"/>
+      <c r="J694" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K694" s="8"/>
       <c r="L694" s="8"/>
     </row>
@@ -26886,7 +28292,9 @@
       <c r="G695" s="3"/>
       <c r="H695" s="4"/>
       <c r="I695" s="4"/>
-      <c r="J695" s="7"/>
+      <c r="J695" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K695" s="8"/>
       <c r="L695" s="8"/>
     </row>
@@ -26910,7 +28318,9 @@
       <c r="G696" s="3"/>
       <c r="H696" s="4"/>
       <c r="I696" s="4"/>
-      <c r="J696" s="7"/>
+      <c r="J696" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K696" s="8"/>
       <c r="L696" s="8"/>
     </row>
@@ -26936,7 +28346,9 @@
       <c r="G697" s="3"/>
       <c r="H697" s="4"/>
       <c r="I697" s="4"/>
-      <c r="J697" s="7"/>
+      <c r="J697" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K697" s="8"/>
       <c r="L697" s="8"/>
     </row>
@@ -26960,7 +28372,9 @@
       <c r="G698" s="3"/>
       <c r="H698" s="4"/>
       <c r="I698" s="4"/>
-      <c r="J698" s="7"/>
+      <c r="J698" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K698" s="8"/>
       <c r="L698" s="8"/>
     </row>
@@ -26984,7 +28398,9 @@
       <c r="G699" s="3"/>
       <c r="H699" s="4"/>
       <c r="I699" s="4"/>
-      <c r="J699" s="7"/>
+      <c r="J699" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K699" s="8"/>
       <c r="L699" s="8"/>
     </row>
@@ -27008,7 +28424,9 @@
       <c r="G700" s="3"/>
       <c r="H700" s="4"/>
       <c r="I700" s="4"/>
-      <c r="J700" s="7"/>
+      <c r="J700" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K700" s="8"/>
       <c r="L700" s="8"/>
     </row>
@@ -27032,7 +28450,9 @@
       <c r="G701" s="3"/>
       <c r="H701" s="4"/>
       <c r="I701" s="4"/>
-      <c r="J701" s="7"/>
+      <c r="J701" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K701" s="8"/>
       <c r="L701" s="8"/>
     </row>
@@ -27058,7 +28478,9 @@
       <c r="G702" s="3"/>
       <c r="H702" s="4"/>
       <c r="I702" s="4"/>
-      <c r="J702" s="7"/>
+      <c r="J702" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K702" s="8"/>
       <c r="L702" s="8"/>
     </row>
@@ -27084,7 +28506,9 @@
       <c r="G703" s="3"/>
       <c r="H703" s="4"/>
       <c r="I703" s="4"/>
-      <c r="J703" s="7"/>
+      <c r="J703" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K703" s="8"/>
       <c r="L703" s="8"/>
     </row>
@@ -27110,7 +28534,9 @@
       <c r="G704" s="3"/>
       <c r="H704" s="4"/>
       <c r="I704" s="4"/>
-      <c r="J704" s="7"/>
+      <c r="J704" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K704" s="8"/>
       <c r="L704" s="8"/>
     </row>
@@ -27134,7 +28560,9 @@
       <c r="G705" s="3"/>
       <c r="H705" s="4"/>
       <c r="I705" s="4"/>
-      <c r="J705" s="7"/>
+      <c r="J705" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K705" s="8"/>
       <c r="L705" s="8"/>
     </row>
@@ -27158,7 +28586,9 @@
       <c r="G706" s="3"/>
       <c r="H706" s="4"/>
       <c r="I706" s="4"/>
-      <c r="J706" s="7"/>
+      <c r="J706" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K706" s="8"/>
       <c r="L706" s="8"/>
     </row>
@@ -27182,7 +28612,9 @@
       <c r="G707" s="3"/>
       <c r="H707" s="4"/>
       <c r="I707" s="4"/>
-      <c r="J707" s="7"/>
+      <c r="J707" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K707" s="8"/>
       <c r="L707" s="8"/>
     </row>
@@ -27212,7 +28644,9 @@
         <v>2416</v>
       </c>
       <c r="I708" s="4"/>
-      <c r="J708" s="7"/>
+      <c r="J708" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K708" s="8"/>
       <c r="L708" s="8"/>
     </row>
@@ -27238,7 +28672,9 @@
       <c r="G709" s="3"/>
       <c r="H709" s="4"/>
       <c r="I709" s="4"/>
-      <c r="J709" s="7"/>
+      <c r="J709" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K709" s="8"/>
       <c r="L709" s="8"/>
     </row>
@@ -27264,7 +28700,9 @@
       <c r="G710" s="3"/>
       <c r="H710" s="4"/>
       <c r="I710" s="4"/>
-      <c r="J710" s="7"/>
+      <c r="J710" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K710" s="8"/>
       <c r="L710" s="8"/>
     </row>
@@ -27288,7 +28726,9 @@
       <c r="G711" s="3"/>
       <c r="H711" s="4"/>
       <c r="I711" s="4"/>
-      <c r="J711" s="7"/>
+      <c r="J711" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K711" s="8"/>
       <c r="L711" s="8"/>
     </row>
@@ -27312,7 +28752,9 @@
       <c r="G712" s="3"/>
       <c r="H712" s="4"/>
       <c r="I712" s="4"/>
-      <c r="J712" s="7"/>
+      <c r="J712" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K712" s="8"/>
       <c r="L712" s="8"/>
     </row>
@@ -27340,7 +28782,9 @@
         <v>2431</v>
       </c>
       <c r="I713" s="4"/>
-      <c r="J713" s="7"/>
+      <c r="J713" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K713" s="8"/>
       <c r="L713" s="8"/>
     </row>
@@ -27370,7 +28814,9 @@
         <v>2436</v>
       </c>
       <c r="I714" s="4"/>
-      <c r="J714" s="7"/>
+      <c r="J714" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K714" s="8"/>
       <c r="L714" s="8"/>
     </row>
@@ -27396,7 +28842,9 @@
       <c r="G715" s="3"/>
       <c r="H715" s="4"/>
       <c r="I715" s="4"/>
-      <c r="J715" s="7"/>
+      <c r="J715" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K715" s="8"/>
       <c r="L715" s="8"/>
     </row>
@@ -27422,7 +28870,9 @@
       <c r="G716" s="3"/>
       <c r="H716" s="4"/>
       <c r="I716" s="4"/>
-      <c r="J716" s="7"/>
+      <c r="J716" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K716" s="8"/>
       <c r="L716" s="8"/>
     </row>
@@ -27446,7 +28896,9 @@
       <c r="G717" s="3"/>
       <c r="H717" s="4"/>
       <c r="I717" s="4"/>
-      <c r="J717" s="7"/>
+      <c r="J717" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K717" s="8"/>
       <c r="L717" s="8"/>
     </row>
@@ -27472,8 +28924,12 @@
       <c r="G718" s="3"/>
       <c r="H718" s="4"/>
       <c r="I718" s="4"/>
-      <c r="J718" s="7"/>
-      <c r="K718" s="8"/>
+      <c r="J718" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K718" s="8" t="s">
+        <v>2622</v>
+      </c>
       <c r="L718" s="8"/>
     </row>
     <row r="719" spans="1:12" x14ac:dyDescent="0.2">
@@ -27496,7 +28952,9 @@
       <c r="G719" s="3"/>
       <c r="H719" s="4"/>
       <c r="I719" s="4"/>
-      <c r="J719" s="7"/>
+      <c r="J719" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K719" s="8"/>
       <c r="L719" s="8"/>
     </row>
@@ -27522,7 +28980,9 @@
       <c r="G720" s="3"/>
       <c r="H720" s="4"/>
       <c r="I720" s="4"/>
-      <c r="J720" s="7"/>
+      <c r="J720" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K720" s="8"/>
       <c r="L720" s="8"/>
     </row>
@@ -27546,7 +29006,9 @@
       <c r="G721" s="3"/>
       <c r="H721" s="4"/>
       <c r="I721" s="4"/>
-      <c r="J721" s="7"/>
+      <c r="J721" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K721" s="8"/>
       <c r="L721" s="8"/>
     </row>
@@ -27570,7 +29032,9 @@
       <c r="G722" s="3"/>
       <c r="H722" s="4"/>
       <c r="I722" s="4"/>
-      <c r="J722" s="7"/>
+      <c r="J722" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K722" s="8"/>
       <c r="L722" s="8"/>
     </row>
@@ -27594,7 +29058,9 @@
       <c r="G723" s="3"/>
       <c r="H723" s="4"/>
       <c r="I723" s="4"/>
-      <c r="J723" s="7"/>
+      <c r="J723" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K723" s="8"/>
       <c r="L723" s="8"/>
     </row>
@@ -27618,7 +29084,9 @@
       <c r="G724" s="3"/>
       <c r="H724" s="4"/>
       <c r="I724" s="4"/>
-      <c r="J724" s="7"/>
+      <c r="J724" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K724" s="8"/>
       <c r="L724" s="8"/>
     </row>
@@ -27642,7 +29110,9 @@
       <c r="G725" s="3"/>
       <c r="H725" s="4"/>
       <c r="I725" s="4"/>
-      <c r="J725" s="7"/>
+      <c r="J725" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K725" s="8"/>
       <c r="L725" s="8"/>
     </row>
@@ -27666,7 +29136,9 @@
       <c r="G726" s="3"/>
       <c r="H726" s="4"/>
       <c r="I726" s="4"/>
-      <c r="J726" s="7"/>
+      <c r="J726" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K726" s="8"/>
       <c r="L726" s="8"/>
     </row>
@@ -27690,7 +29162,9 @@
       <c r="G727" s="3"/>
       <c r="H727" s="4"/>
       <c r="I727" s="4"/>
-      <c r="J727" s="7"/>
+      <c r="J727" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K727" s="8"/>
       <c r="L727" s="8"/>
     </row>
@@ -27714,7 +29188,9 @@
       <c r="G728" s="3"/>
       <c r="H728" s="4"/>
       <c r="I728" s="4"/>
-      <c r="J728" s="7"/>
+      <c r="J728" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K728" s="8"/>
       <c r="L728" s="8"/>
     </row>
@@ -27738,7 +29214,9 @@
       <c r="G729" s="3"/>
       <c r="H729" s="4"/>
       <c r="I729" s="4"/>
-      <c r="J729" s="7"/>
+      <c r="J729" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K729" s="8"/>
       <c r="L729" s="8"/>
     </row>
@@ -27762,7 +29240,9 @@
       <c r="G730" s="3"/>
       <c r="H730" s="4"/>
       <c r="I730" s="4"/>
-      <c r="J730" s="7"/>
+      <c r="J730" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K730" s="8"/>
       <c r="L730" s="8"/>
     </row>
@@ -27786,7 +29266,9 @@
       <c r="G731" s="3"/>
       <c r="H731" s="4"/>
       <c r="I731" s="4"/>
-      <c r="J731" s="7"/>
+      <c r="J731" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K731" s="8"/>
       <c r="L731" s="8"/>
     </row>
@@ -27810,7 +29292,9 @@
       <c r="G732" s="3"/>
       <c r="H732" s="4"/>
       <c r="I732" s="4"/>
-      <c r="J732" s="7"/>
+      <c r="J732" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K732" s="8"/>
       <c r="L732" s="8"/>
     </row>
@@ -27834,7 +29318,9 @@
       <c r="G733" s="3"/>
       <c r="H733" s="4"/>
       <c r="I733" s="4"/>
-      <c r="J733" s="7"/>
+      <c r="J733" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K733" s="8"/>
       <c r="L733" s="8"/>
     </row>
@@ -27858,7 +29344,9 @@
       <c r="G734" s="3"/>
       <c r="H734" s="4"/>
       <c r="I734" s="4"/>
-      <c r="J734" s="7"/>
+      <c r="J734" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K734" s="8"/>
       <c r="L734" s="8"/>
     </row>
@@ -27882,7 +29370,9 @@
       <c r="G735" s="3"/>
       <c r="H735" s="4"/>
       <c r="I735" s="4"/>
-      <c r="J735" s="7"/>
+      <c r="J735" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K735" s="8"/>
       <c r="L735" s="8"/>
     </row>
@@ -27906,7 +29396,9 @@
       <c r="G736" s="3"/>
       <c r="H736" s="4"/>
       <c r="I736" s="4"/>
-      <c r="J736" s="7"/>
+      <c r="J736" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K736" s="8"/>
       <c r="L736" s="8"/>
     </row>
@@ -27930,7 +29422,9 @@
       <c r="G737" s="3"/>
       <c r="H737" s="4"/>
       <c r="I737" s="4"/>
-      <c r="J737" s="7"/>
+      <c r="J737" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K737" s="8"/>
       <c r="L737" s="8"/>
     </row>
@@ -27954,7 +29448,9 @@
       <c r="G738" s="3"/>
       <c r="H738" s="4"/>
       <c r="I738" s="4"/>
-      <c r="J738" s="7"/>
+      <c r="J738" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K738" s="8"/>
       <c r="L738" s="8"/>
     </row>
@@ -27978,7 +29474,9 @@
       <c r="G739" s="3"/>
       <c r="H739" s="4"/>
       <c r="I739" s="4"/>
-      <c r="J739" s="7"/>
+      <c r="J739" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K739" s="8"/>
       <c r="L739" s="8"/>
     </row>
@@ -28002,7 +29500,9 @@
       <c r="G740" s="3"/>
       <c r="H740" s="4"/>
       <c r="I740" s="4"/>
-      <c r="J740" s="7"/>
+      <c r="J740" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K740" s="8"/>
       <c r="L740" s="8"/>
     </row>
@@ -28026,7 +29526,9 @@
       <c r="G741" s="3"/>
       <c r="H741" s="4"/>
       <c r="I741" s="4"/>
-      <c r="J741" s="7"/>
+      <c r="J741" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K741" s="8"/>
       <c r="L741" s="8"/>
     </row>
@@ -28050,7 +29552,9 @@
       <c r="G742" s="3"/>
       <c r="H742" s="4"/>
       <c r="I742" s="4"/>
-      <c r="J742" s="7"/>
+      <c r="J742" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K742" s="8"/>
       <c r="L742" s="8"/>
     </row>
@@ -28078,7 +29582,9 @@
         <v>2523</v>
       </c>
       <c r="I743" s="4"/>
-      <c r="J743" s="7"/>
+      <c r="J743" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K743" s="8"/>
       <c r="L743" s="8"/>
     </row>
@@ -28106,7 +29612,9 @@
         <v>830</v>
       </c>
       <c r="I744" s="4"/>
-      <c r="J744" s="7"/>
+      <c r="J744" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K744" s="8"/>
       <c r="L744" s="8"/>
     </row>
@@ -28130,7 +29638,9 @@
       <c r="G745" s="3"/>
       <c r="H745" s="4"/>
       <c r="I745" s="4"/>
-      <c r="J745" s="7"/>
+      <c r="J745" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K745" s="8"/>
       <c r="L745" s="8"/>
     </row>
@@ -28154,7 +29664,9 @@
       <c r="G746" s="3"/>
       <c r="H746" s="4"/>
       <c r="I746" s="4"/>
-      <c r="J746" s="7"/>
+      <c r="J746" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K746" s="8"/>
       <c r="L746" s="8"/>
     </row>
@@ -28178,7 +29690,9 @@
       <c r="G747" s="3"/>
       <c r="H747" s="4"/>
       <c r="I747" s="4"/>
-      <c r="J747" s="7"/>
+      <c r="J747" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K747" s="8"/>
       <c r="L747" s="8"/>
     </row>
@@ -28202,7 +29716,9 @@
       <c r="G748" s="3"/>
       <c r="H748" s="4"/>
       <c r="I748" s="4"/>
-      <c r="J748" s="7"/>
+      <c r="J748" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K748" s="8"/>
       <c r="L748" s="8"/>
     </row>
@@ -28232,7 +29748,9 @@
       <c r="I749" s="10" t="s">
         <v>2543</v>
       </c>
-      <c r="J749" s="7"/>
+      <c r="J749" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K749" s="8"/>
       <c r="L749" s="8"/>
     </row>
@@ -28256,7 +29774,9 @@
       <c r="G750" s="3"/>
       <c r="H750" s="4"/>
       <c r="I750" s="4"/>
-      <c r="J750" s="7"/>
+      <c r="J750" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K750" s="8"/>
       <c r="L750" s="8"/>
     </row>
@@ -28280,7 +29800,9 @@
       <c r="G751" s="3"/>
       <c r="H751" s="4"/>
       <c r="I751" s="4"/>
-      <c r="J751" s="7"/>
+      <c r="J751" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K751" s="8"/>
       <c r="L751" s="8"/>
     </row>
@@ -28304,7 +29826,9 @@
       <c r="G752" s="3"/>
       <c r="H752" s="4"/>
       <c r="I752" s="4"/>
-      <c r="J752" s="7"/>
+      <c r="J752" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K752" s="8"/>
       <c r="L752" s="8"/>
     </row>
@@ -28332,7 +29856,9 @@
         <v>2551</v>
       </c>
       <c r="I753" s="4"/>
-      <c r="J753" s="7"/>
+      <c r="J753" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K753" s="8"/>
       <c r="L753" s="8"/>
     </row>
@@ -28360,7 +29886,9 @@
         <v>830</v>
       </c>
       <c r="I754" s="4"/>
-      <c r="J754" s="7"/>
+      <c r="J754" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K754" s="8"/>
       <c r="L754" s="8"/>
     </row>
@@ -28384,7 +29912,9 @@
       <c r="G755" s="3"/>
       <c r="H755" s="4"/>
       <c r="I755" s="4"/>
-      <c r="J755" s="7"/>
+      <c r="J755" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K755" s="8"/>
       <c r="L755" s="8"/>
     </row>
@@ -28412,7 +29942,9 @@
         <v>830</v>
       </c>
       <c r="I756" s="4"/>
-      <c r="J756" s="7"/>
+      <c r="J756" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K756" s="8"/>
       <c r="L756" s="8"/>
     </row>
@@ -28436,7 +29968,9 @@
       <c r="G757" s="3"/>
       <c r="H757" s="4"/>
       <c r="I757" s="4"/>
-      <c r="J757" s="7"/>
+      <c r="J757" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K757" s="8"/>
       <c r="L757" s="8"/>
     </row>
@@ -28460,7 +29994,9 @@
       <c r="G758" s="3"/>
       <c r="H758" s="4"/>
       <c r="I758" s="4"/>
-      <c r="J758" s="7"/>
+      <c r="J758" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K758" s="8"/>
       <c r="L758" s="8"/>
     </row>
@@ -28484,7 +30020,9 @@
       <c r="G759" s="3"/>
       <c r="H759" s="4"/>
       <c r="I759" s="4"/>
-      <c r="J759" s="7"/>
+      <c r="J759" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K759" s="8"/>
       <c r="L759" s="8"/>
     </row>
@@ -28508,7 +30046,9 @@
       <c r="G760" s="3"/>
       <c r="H760" s="4"/>
       <c r="I760" s="4"/>
-      <c r="J760" s="7"/>
+      <c r="J760" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K760" s="8"/>
       <c r="L760" s="8"/>
     </row>
@@ -28532,7 +30072,9 @@
       <c r="G761" s="3"/>
       <c r="H761" s="4"/>
       <c r="I761" s="4"/>
-      <c r="J761" s="7"/>
+      <c r="J761" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K761" s="8"/>
       <c r="L761" s="8"/>
     </row>
@@ -28556,7 +30098,9 @@
       <c r="G762" s="3"/>
       <c r="H762" s="4"/>
       <c r="I762" s="4"/>
-      <c r="J762" s="7"/>
+      <c r="J762" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K762" s="8"/>
       <c r="L762" s="8"/>
     </row>
@@ -28580,7 +30124,9 @@
       <c r="G763" s="3"/>
       <c r="H763" s="4"/>
       <c r="I763" s="4"/>
-      <c r="J763" s="7"/>
+      <c r="J763" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K763" s="8"/>
       <c r="L763" s="8"/>
     </row>
@@ -28604,7 +30150,9 @@
       <c r="G764" s="3"/>
       <c r="H764" s="4"/>
       <c r="I764" s="4"/>
-      <c r="J764" s="7"/>
+      <c r="J764" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K764" s="8"/>
       <c r="L764" s="8"/>
     </row>
@@ -28628,7 +30176,9 @@
       <c r="G765" s="3"/>
       <c r="H765" s="4"/>
       <c r="I765" s="4"/>
-      <c r="J765" s="7"/>
+      <c r="J765" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K765" s="8"/>
       <c r="L765" s="8"/>
     </row>
@@ -28652,7 +30202,9 @@
       <c r="G766" s="3"/>
       <c r="H766" s="4"/>
       <c r="I766" s="4"/>
-      <c r="J766" s="7"/>
+      <c r="J766" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K766" s="8"/>
       <c r="L766" s="8"/>
     </row>
@@ -28676,7 +30228,9 @@
       <c r="G767" s="3"/>
       <c r="H767" s="4"/>
       <c r="I767" s="4"/>
-      <c r="J767" s="7"/>
+      <c r="J767" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K767" s="8"/>
       <c r="L767" s="8"/>
     </row>
@@ -28700,7 +30254,9 @@
       <c r="G768" s="3"/>
       <c r="H768" s="4"/>
       <c r="I768" s="4"/>
-      <c r="J768" s="7"/>
+      <c r="J768" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K768" s="8"/>
       <c r="L768" s="8"/>
     </row>
@@ -28726,7 +30282,9 @@
       <c r="I769" s="10" t="s">
         <v>2593</v>
       </c>
-      <c r="J769" s="7"/>
+      <c r="J769" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K769" s="8"/>
       <c r="L769" s="8"/>
     </row>
@@ -28754,11 +30312,15 @@
         <v>2596</v>
       </c>
       <c r="I770" s="4"/>
-      <c r="J770" s="7"/>
-      <c r="K770" s="8"/>
+      <c r="J770" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K770" s="8" t="s">
+        <v>2623</v>
+      </c>
       <c r="L770" s="8"/>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A771" s="3" t="s">
         <v>1389</v>
       </c>
@@ -28778,8 +30340,12 @@
       <c r="G771" s="3"/>
       <c r="H771" s="4"/>
       <c r="I771" s="4"/>
-      <c r="J771" s="7"/>
-      <c r="K771" s="8"/>
+      <c r="J771" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K771" s="8" t="s">
+        <v>2624</v>
+      </c>
       <c r="L771" s="8"/>
     </row>
     <row r="772" spans="1:12" x14ac:dyDescent="0.2">
@@ -28802,7 +30368,9 @@
       <c r="G772" s="3"/>
       <c r="H772" s="4"/>
       <c r="I772" s="4"/>
-      <c r="J772" s="7"/>
+      <c r="J772" s="7" t="s">
+        <v>2057</v>
+      </c>
       <c r="K772" s="8"/>
       <c r="L772" s="8"/>
     </row>
@@ -28826,8 +30394,12 @@
       <c r="G773" s="3"/>
       <c r="H773" s="4"/>
       <c r="I773" s="4"/>
-      <c r="J773" s="7"/>
-      <c r="K773" s="8"/>
+      <c r="J773" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K773" s="8" t="s">
+        <v>2625</v>
+      </c>
       <c r="L773" s="8"/>
     </row>
     <row r="774" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
@@ -28852,8 +30424,12 @@
       <c r="I774" s="10" t="s">
         <v>2607</v>
       </c>
-      <c r="J774" s="7"/>
-      <c r="K774" s="8"/>
+      <c r="J774" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K774" s="8" t="s">
+        <v>2626</v>
+      </c>
       <c r="L774" s="8"/>
     </row>
     <row r="775" spans="1:12" x14ac:dyDescent="0.2">
@@ -28876,8 +30452,12 @@
       <c r="G775" s="3"/>
       <c r="H775" s="4"/>
       <c r="I775" s="4"/>
-      <c r="J775" s="7"/>
-      <c r="K775" s="8"/>
+      <c r="J775" s="7" t="s">
+        <v>2621</v>
+      </c>
+      <c r="K775" s="8" t="s">
+        <v>2623</v>
+      </c>
       <c r="L775" s="8"/>
     </row>
   </sheetData>
